--- a/Data/WorldTop.xlsx
+++ b/Data/WorldTop.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,1131 +467,1131 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What was the world's first message sent over the internet?</t>
+          <t>Which is the largest ocean in the world by area?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which country launched the world's first satellite?</t>
+          <t>What was the first online shopping site?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>NetMarket</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>NetMarket</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What was the first ever video uploaded to YouTube?</t>
+          <t>Which was the first Indian state formed on linguistic basis?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hello World</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Test Video</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Launch Video</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which was the first country to grant women the right to vote?</t>
+          <t>Which is the largest island in the world?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New Guinea</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Greenland</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What was the name of the first computer virus?</t>
+          <t>What was the first website ever created?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ILOVEYOU</t>
+          <t>Google.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>Wikipedia.org</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuxnet</t>
+          <t>CERN.ch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WannaCry</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who was the first person to step on the Moon?</t>
+          <t>Who was the first Indian female IPS officer?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Anu Singh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Radhika Kumari</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Michael Collins</t>
+          <t>Pooja Thakur</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What was the first cloned mammal?</t>
+          <t>Which is the first Indian bank to launch an ATM?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Molly the Cow</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Polly the Pig</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>ICICI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kitty the Cat</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>HSBC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which was the first movie with sound (talkie)?</t>
+          <t>Who was the first woman Prime Minister in the world?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>King Kong</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Golda Meir</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What was the first smartphone ever made?</t>
+          <t>Which animal is considered the fastest on land?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nokia 3310</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motorola DynaTAC</t>
+          <t>Greyhound</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>Cheetah</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which was the first country to legalize same-sex marriage?</t>
+          <t>Which is the fastest bird in the world?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Golden Eagle</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Swan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which was the first country to use paper money?</t>
+          <t>Which country has the most lakes?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Who invented the first telephone?</t>
+          <t>Which is the most downloaded app of all time?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guglielmo Marconi</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which was the world's first artificial satellite?</t>
+          <t>Which is the world’s oldest living city?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apollo 11</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luna 2</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Varanasi</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What was the first email ever sent?</t>
+          <t>Which was the first car manufacturing company?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>Peugeot</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Login123</t>
+          <t>Rolls-Royce</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>Peugeot</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who was the first woman to win a Nobel Prize?</t>
+          <t>Which is the smallest mammal by weight?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rosalind Franklin</t>
+          <t>Pygmy Shrew</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Mouse Lemur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Pygmy Possum</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which is the first country to adopt a national flag?</t>
+          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Gangtok</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Gangtok</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What was the first video game ever created?</t>
+          <t>Which is the richest company in the world by market value (2025)?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pac-Man</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tetris</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which was the first human-made object to reach space?</t>
+          <t>Who invented the first electric light bulb?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Michael Faraday</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What was the first website ever created?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Google.com</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wikipedia.org</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CERN.ch</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which was the first animated feature film?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cinderella</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pinocchio</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bambi</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Who was the first human in space?</t>
+          <t>Which country exports the most weapons?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which was the first programming language?</t>
+          <t>Which country has the largest forest area in the world?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>COBOL</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who invented the first airplane?</t>
+          <t>Which is the world's first language (known oldest)?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Charles Lindbergh</t>
+          <t>Sumerian</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>Sumerian</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What was the first country to recognize the United States as independent?</t>
+          <t>Which is the most spoken language in India?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>English</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Hindi</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What was the first successful vaccine developed for?</t>
+          <t>Which is the world’s first country to ban tobacco completely?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>Bhutan</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which was the first city to host the modern Olympic Games?</t>
+          <t>Which bird is believed to be extinct due to human activity?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Penguin</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Bald Eagle</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Dodo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Dodo</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which was the first nation to reach the South Pole?</t>
+          <t>What was the first cloned mammal?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Molly the Cow</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Polly the Pig</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Kitty the Cat</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What was the first object sold on eBay?</t>
+          <t>Which is the deepest ocean in the world?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wristwatch</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Comic Book</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which was the first car manufacturing company?</t>
+          <t>Who was the first person to go to space?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rolls-Royce</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What was the first country to ban plastic bags nationwide?</t>
+          <t>Which is the smallest country in the world by land area?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What was the first computer called?</t>
+          <t>What was the first country to recognize the United States as independent?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IBM 1401</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Apple I</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>Morocco</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Who was the first person to win two Nobel Prizes?</t>
+          <t>Who was the first woman ruler of India?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Albert Einstein</t>
+          <t>Rani Lakshmibai</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Linus Pauling</t>
+          <t>Ahilyabai Holkar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erwin Schrödinger</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which was the first country to reach Mars orbit successfully?</t>
+          <t>Which country produces the most oil?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,1697 +1606,1697 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which was the first messaging app?</t>
+          <t>Which is the highest waterfall in the world?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Niagara Falls</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>Tugela Falls</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AIM</t>
+          <t>Angel Falls</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Yosemite Falls</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>Angel Falls</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What was the first online shopping site?</t>
+          <t>Which was the first Indian company listed on NASDAQ?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Satyam</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Infosys</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who was the first President of the world’s first republic (USA)?</t>
+          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>Dorothy Hodgkin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>John Adams</t>
+          <t>Lise Meitner</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of the United Kingdom?</t>
+          <t>Who was the first woman to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>Rosalind Franklin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tony Blair</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of India?</t>
+          <t>Which is the first Indian mission to Mars?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sardar Patel</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>IRNSS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Who was the first President of India?</t>
+          <t>Which was the first country to legalize same-sex marriage?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dr. S. Radhakrishnan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Netherlands</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What is the world’s tallest statue as of 2025?</t>
+          <t>Who was the first Indian Miss World?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Sushmita Sen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Lara Dutta</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>Reita Faria</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Aishwarya Rai</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Reita Faria</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which is the tallest building in the world?</t>
+          <t>Which city is known as the "Silicon Valley of India"?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shanghai Tower</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Merdeka 118</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>One World Trade Center</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>Bangalore</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
+          <t>Who is the first Indian to climb Mount Everest?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Titanic</t>
+          <t>Bachendri Pal</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>Tenzing Norgay</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Avengers: Endgame</t>
+          <t>Santosh Yadav</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oppenheimer</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which is the world’s first programmable computer?</t>
+          <t>Which was the first Indian communication satellite?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Colossus</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>APPLESAT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>INSAT-2A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which is the world’s first university?</t>
+          <t>Which is the largest continent by land area?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nalanda</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al-Qarawiyyin</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Who was the first woman Prime Minister in the world?</t>
+          <t>Which is the longest river in the world?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Golda Meir</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>Nile</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which is the world's most visited heritage site?</t>
+          <t>Which Indian city is known as the 'City of Lakes'?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Eiffel Tower</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colosseum</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>Udaipur</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>Which Indian river got the status of ‘living entity’ first?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Ganga</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Who was the first person to receive Bharat Ratna?</t>
+          <t>Which was the first Indian city to be electrified?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>S. Radhakrishnan</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Darjeeling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Darjeeling</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who was India’s first female President?</t>
+          <t>Which was the world's first artificial satellite?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Apollo 11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>Luna 2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What is the name of India’s first satellite?</t>
+          <t>Which country has the most nuclear weapons as of 2025?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chandrayaan</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Who was the first person to go to space?</t>
+          <t>Which is the smallest state in India by area?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Goa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which is the first country to implement a constitution?</t>
+          <t>Which is the largest freshwater lake in the world by surface area?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Lake Victoria</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Lake Superior</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which is the world’s oldest living city?</t>
+          <t>Which was the first movie with sound (talkie)?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>King Kong</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which is the first country to launch a digital currency?</t>
+          <t>Which was the first city to host the modern Olympic Games?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which is the world's first man-made nuclear reactor?</t>
+          <t>Which country has the largest economy (GDP)?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fermi-1</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DIDO</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>THTR-300</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to achieve 100% literacy?</t>
+          <t>Which was the first Indian movie submitted for the Oscars?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Mother India</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which is the world’s first democracy?</t>
+          <t>Who was the first woman to fly solo around the world?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Valentina Tereshkova</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Anne Morrow</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who was the first Indian in space?</t>
+          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>IIT Delhi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>IIT Bombay</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>IIT Madras</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which is India’s first supercomputer?</t>
+          <t>Who was the first female Prime Minister of India?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Shakti</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Virgo</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mihir</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the "first Smart City"?</t>
+          <t>Which was the first Indian satellite to orbit the Moon?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman in space?</t>
+          <t>Which Indian state has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ritu Karidhal</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which was the first Indian satellite to orbit the Moon?</t>
+          <t>Which is the smallest bone in the human body?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Femur</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Tibia</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Stapes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>Ulna</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Stapes</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a Nobel Prize?</t>
+          <t>Which planet has the most moons?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>C.V. Raman</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Saturn</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which is the world's first language (known oldest)?</t>
+          <t>Which is the longest railway platform in the world?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Gorakhpur</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Kharagpur</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Hubballi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>Howrah</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>Hubballi</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which is the first Indian state to ban plastic completely?</t>
+          <t>Who was the first Indian in space?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Who was the first woman to fly solo around the world?</t>
+          <t>Which was the first Indian film to win an Oscar?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Valentina Tereshkova</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Slumdog Millionaire</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anne Morrow</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Gandhi</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which is the world's first novel ever written?</t>
+          <t>Which Indian river has the largest length within India?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Don Quixote</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Beowulf</t>
+          <t>Brahmaputra</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>Ganga</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to get an underground metro?</t>
+          <t>Which country has the most time zones (including territories)?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who is the first Indian to climb Mount Everest?</t>
+          <t>Which country has the highest GDP in the world?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bachendri Pal</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tenzing Norgay</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Santosh Yadav</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
+          <t>Who invented the first telephone?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunil Gavaskar</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Alexander Graham Bell</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sachin Tendulkar</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rahul Dravid</t>
+          <t>Guglielmo Marconi</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Alexander Graham Bell</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which was the first Indian film to win an Oscar?</t>
+          <t>Which was the first programming language?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>COBOL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Slumdog Millionaire</t>
+          <t>Fortran</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Assembly</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Fortran</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Who invented the first electric light bulb?</t>
+          <t>Who was India’s first female President?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Michael Faraday</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a monorail?</t>
+          <t>Who was the first President of the world’s first republic (USA)?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>George Washington</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>John Adams</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>George Washington</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
+          <t>Which is the largest state in India by area?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dorothy Hodgkin</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lise Meitner</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Rajasthan</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Indian was the first to win an Olympic gold medal?</t>
+          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Major Dhyan Chand</t>
+          <t>Amartya Sen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KD Jadhav</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which is the first Indian mission to Mars?</t>
+          <t>Who was the first person to step on the Moon?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>IRNSS</t>
+          <t>Michael Collins</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Who was the first woman ruler of India?</t>
+          <t>Which is the largest dam in India by volume?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rani Lakshmibai</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>Sardar Sarovar Dam</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ahilyabai Holkar</t>
+          <t>Bhakra Nangal</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which was the first Indian film?</t>
+          <t>Which country has the highest number of billionaires?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alam Ara</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sholay</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which Indian state hosted the first International G20 summit in India?</t>
+          <t>Which is the world’s first democracy?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What is India’s first nuclear reactor called?</t>
+          <t>What was the world's first message sent over the internet?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dhruva</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KAMINI</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>LO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CIRUS</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>LO</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which was the first Indian express train?</t>
+          <t>Which is the highest mountain peak in the world?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Shatabdi Express</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Rajdhani Express</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Duronto Express</t>
+          <t>Makalu</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>Mount Everest</t>
         </is>
       </c>
     </row>
@@ -3306,767 +3306,767 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Who was the first Indian female IPS officer?</t>
+          <t>Which is the most spoken language in the world?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Anu Singh</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Radhika Kumari</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pooja Thakur</t>
+          <t>Mandarin</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What was the world’s first search engine?</t>
+          <t>Which Indian state hosted the first International G20 summit in India?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AltaVista</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank?</t>
+          <t>Who was the first human in space?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Allahabad Bank</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which Indian city is the first to use electric buses at scale?</t>
+          <t>Which Indian state launched the first electric vehicle policy?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Karnataka</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
+          <t>Who was the first Prime Minister of the United Kingdom?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IIT Delhi</t>
+          <t>Winston Churchill</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>IIT Bombay</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>IIT Madras</t>
+          <t>Tony Blair</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Who was the first Indian Governor-General of independent India?</t>
+          <t>Which is the world's most visited heritage site?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lord Mountbatten</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Eiffel Tower</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Colosseum</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which was the first war of Indian independence?</t>
+          <t>Which is the tallest statue in the world?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Battle of Plassey</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Battle of Panipat</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Who was the first female Prime Minister of India?</t>
+          <t>Which is the first Indian city to have a monorail?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Mumbai</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>What was the first biosphere reserve in India?</t>
+          <t>Which is the smallest bird in the world?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sundarbans</t>
+          <t>Hummingbird</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>Parakeet</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nanda Devi</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Manas</t>
+          <t>Finch</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>Hummingbird</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which was the first Indian city to be electrified?</t>
+          <t>Which is the most populated city in the world?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>Tokyo</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which was the first Indian communication satellite?</t>
+          <t>Which is the world's first man-made nuclear reactor?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Fermi-1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>APPLESAT</t>
+          <t>DIDO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>INSAT-2A</t>
+          <t>THTR-300</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
+          <t>Which is the deepest lake in the world?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Saina Nehwal</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P. V. Sindhu</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mary Kom</t>
+          <t>Caspian Sea</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which was the first Indian company listed on NASDAQ?</t>
+          <t>Which religion has the most followers in the world?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Christianity</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Islam</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Satyam</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Christianity</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
+          <t>What was the name of the first computer virus?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>ILOVEYOU</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Neeraj Chopra</t>
+          <t>Creeper</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hima Das</t>
+          <t>Stuxnet</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anju George</t>
+          <t>WannaCry</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>Creeper</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to implement the GST?</t>
+          <t>Which city has the most skyscrapers (over 150m)?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Hong Kong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which is India’s first indigenously built aircraft carrier?</t>
+          <t>Which is the longest national highway in India?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>NH44</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>INS Viraat</t>
+          <t>NH7</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>INS Arihant</t>
+          <t>NH27</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>INS Trikand</t>
+          <t>NH19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>NH44</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
+          <t>Which is the tallest animal in the world?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>General V. K. Singh</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>General Manoj Pande</t>
+          <t>Camel</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Admiral Karambir Singh</t>
+          <t>Moose</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>Giraffe</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a fully underground metro network?</t>
+          <t>What was the world’s first printed book?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>The Holy Bible</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Quran</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which Indian river got the status of ‘living entity’ first?</t>
+          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Titanic</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Avatar</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Avengers: Endgame</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Oppenheimer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Avatar</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which is the world’s first country to ban tobacco completely?</t>
+          <t>Which is the most visited city in the world (tourism)?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Paris</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>What was the world’s first printed book?</t>
+          <t>Which mobile phone brand sells the most globally?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>The Holy Bible</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Quran</t>
+          <t>Oppo</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Who was the first Indian Miss World?</t>
+          <t>What was the first computer called?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sushmita Sen</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Lara Dutta</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>IBM 1401</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aishwarya Rai</t>
+          <t>Apple I</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>ENIAC</t>
         </is>
       </c>
     </row>
@@ -4076,382 +4076,382 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
+          <t>Which river carries the most water by volume?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which was the first Indian state formed on linguistic basis?</t>
+          <t>Which Indian airport is the busiest by passenger traffic?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Kempegowda Intl (Bangalore)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Rajiv Gandhi Intl (Hyderabad)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank to launch an ATM?</t>
+          <t>Who was the first person to win two Nobel Prizes?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>Albert Einstein</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ICICI</t>
+          <t>Linus Pauling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>Erwin Schrödinger</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
+          <t>Which is the largest bird in the world?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Amartya Sen</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Emu</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Ostrich</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which Indian state launched the first electric vehicle policy?</t>
+          <t>Which was the first Indian express train?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Shatabdi Express</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Rajdhani Express</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Duronto Express</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which was the first Indian movie submitted for the Oscars?</t>
+          <t>Which country has the highest population in the world?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Which is the first country to make education compulsory by law?</t>
+          <t>Which country launched the world's first satellite?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which is the deepest ocean in the world?</t>
+          <t>What is the world’s tallest statue as of 2025?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which is the largest ocean in the world by area?</t>
+          <t>Which was the first messaging app?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>ICQ</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>AIM</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>ICQ</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which is the largest continent by land area?</t>
+          <t>Which is the first country to adopt a national flag?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which bird is believed to be extinct due to human activity?</t>
+          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Penguin</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Bald Eagle</t>
+          <t>Saina Nehwal</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>P. V. Sindhu</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Mary Kom</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
     </row>
@@ -4461,417 +4461,417 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which country has the largest number of active military personnel?</t>
+          <t>Which is the first Indian state to ban plastic completely?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Sikkim</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which is the smallest country in the world by land area?</t>
+          <t>Which Indian was the first to win an Olympic gold medal?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Major Dhyan Chand</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>KD Jadhav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which is the longest river in the world?</t>
+          <t>Who was the first Indian to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>C.V. Raman</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which is the highest mountain peak in the world?</t>
+          <t>Which country is the largest producer of gold?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Makalu</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which is the largest desert in the world?</t>
+          <t>Which Indian city is the first to use electric buses at scale?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sahara</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Gobi</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kalahari</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>Pune</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which is the largest island in the world?</t>
+          <t>What was the first country to ban plastic bags nationwide?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>New Guinea</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Rwanda</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which is the fastest bird in the world?</t>
+          <t>Which country has the most volcanoes?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Golden Eagle</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Swan</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which is the largest mammal in the world?</t>
+          <t>Which is the first Indian bank?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>African Elephant</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hippopotamus</t>
+          <t>Allahabad Bank</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which country has the longest coastline?</t>
+          <t>What was the first email ever sent?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Login123</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which is the smallest bone in the human body?</t>
+          <t>Which country has the largest number of active military personnel?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Femur</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tibia</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ulna</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which is the smallest bird in the world?</t>
+          <t>Which is the largest species of shark?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Tiger Shark</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Parakeet</t>
+          <t>Hammerhead Shark</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Whale Shark</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Finch</t>
+          <t>Great White Shark</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Whale Shark</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which country has the highest population in the world?</t>
+          <t>Who was the first Prime Minister of India?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Sardar Patel</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
     </row>
@@ -4881,872 +4881,872 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which is the hottest planet in the solar system?</t>
+          <t>Which is the first country to implement a constitution?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which is the coldest place on Earth?</t>
+          <t>Who was the first Indian woman in space?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Siberia</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Ritu Karidhal</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which is the largest species of shark?</t>
+          <t>Which is India’s first supercomputer?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tiger Shark</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Hammerhead Shark</t>
+          <t>Shakti</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>Virgo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Great White Shark</t>
+          <t>Mihir</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Which is the tallest animal in the world?</t>
+          <t>Which was the first animated feature film?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Cinderella</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Camel</t>
+          <t>Pinocchio</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Moose</t>
+          <t>Bambi</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Which is the smallest mammal by weight?</t>
+          <t>Which is the most used currency in the world?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Pygmy Shrew</t>
+          <t>Yen</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mouse Lemur</t>
+          <t>US Dollar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pygmy Possum</t>
+          <t>Pound Sterling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>US Dollar</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in the world?</t>
+          <t>Which is India’s first indigenously built aircraft carrier?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>INS Viraat</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>INS Arihant</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>INS Trikand</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Which is the most populated city in the world?</t>
+          <t>Who was the first person to receive Bharat Ratna?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>S. Radhakrishnan</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Which planet has the most moons?</t>
+          <t>Which is the largest mosque in India?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Jama Masjid, Delhi</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Mecca Masjid, Hyderabad</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Nakhoda Masjid, Kolkata</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Which is the first artificial satellite sent into space?</t>
+          <t>What was the first successful vaccine developed for?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Vostok</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Smallpox</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Smallpox</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Which is the smallest continent by land area?</t>
+          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Sunil Gavaskar</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sachin Tendulkar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Rahul Dravid</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which is the largest freshwater lake in the world by surface area?</t>
+          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Lake Victoria</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Neeraj Chopra</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Hima Das</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>Anju George</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which is the deepest lake in the world?</t>
+          <t>Which Indian state was the first to implement the GST?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Caspian Sea</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Assam</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which country has the largest forest area in the world?</t>
+          <t>Which is the first artificial satellite sent into space?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Vostok</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Which is the largest country in the world by area?</t>
+          <t>Which is the busiest airport in the world by passenger volume?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Beijing Capital</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Atlanta (ATL)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Heathrow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Dubai Intl</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Atlanta (ATL)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which is the smallest state in India by area?</t>
+          <t>Which is the largest volcano in the world (by volume)?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Mount Fuji</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Eyjafjallajökull</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Mount Etna</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which is the largest state in India by area?</t>
+          <t>Which was the first war of Indian independence?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Battle of Plassey</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Battle of Panipat</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which is the longest national highway in India?</t>
+          <t>Which is the largest mammal in the world?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>African Elephant</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NH7</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>NH27</t>
+          <t>Blue Whale</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NH19</t>
+          <t>Hippopotamus</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>Blue Whale</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Which Indian river has the largest length within India?</t>
+          <t>Which is the smallest continent by land area?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Brahmaputra</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Which is the largest dam in India by volume?</t>
+          <t>Who was the first President of India?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sardar Sarovar Dam</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bhakra Nangal</t>
+          <t>Dr. S. Radhakrishnan</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Which is the largest mosque in India?</t>
+          <t>Which was the first Indian film?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Jama Masjid, Delhi</t>
+          <t>Alam Ara</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Mecca Masjid, Hyderabad</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>Sholay</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Nakhoda Masjid, Kolkata</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the 'City of Lakes'?</t>
+          <t>What is the name of India’s first satellite?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chandrayaan</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Aryabhata</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Which country has the highest GDP in the world?</t>
+          <t>What was the first ever video uploaded to YouTube?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Hello World</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Test Video</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Launch Video</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which is the highest waterfall in the world?</t>
+          <t>Which is the world's first novel ever written?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Niagara Falls</t>
+          <t>Don Quixote</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Tugela Falls</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Yosemite Falls</t>
+          <t>Beowulf</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Which Indian monument has the highest number of tourist visits annually?</t>
+          <t>Which is the most downloaded game of all time?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>PUBG</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Red Fort</t>
+          <t>Candy Crush</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Minecraft</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Which Indian airport is the busiest by passenger traffic?</t>
+          <t>What was the world’s first search engine?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Kempegowda Intl (Bangalore)</t>
+          <t>Archie</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi Intl (Hyderabad)</t>
+          <t>AltaVista</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>Archie</t>
         </is>
       </c>
     </row>
@@ -5756,312 +5756,312 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Which is the longest railway platform in the world?</t>
+          <t>Which was the first nation to reach the South Pole?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Gorakhpur</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Kharagpur</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Norway</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Which country has the smallest population?</t>
+          <t>Which is the largest desert in the world?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Sahara</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Gobi</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Kalahari</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Which country is the largest producer of gold?</t>
+          <t>Which is the coldest place on Earth?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Siberia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Vostok Station</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vostok Station</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Which Indian state has the highest literacy rate?</t>
+          <t>Which is the world’s first programmable computer?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Colossus</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Z3</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Z3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which is the most downloaded app of all time?</t>
+          <t>Which country has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Andorra</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Which planet is closest to Earth most often?</t>
+          <t>What was the first smartphone ever made?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>IBM Simon</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Nokia 3310</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Motorola DynaTAC</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>IBM Simon</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Which is the oldest dam in India still in use?</t>
+          <t>Who invented the first airplane?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mettur Dam</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Krishna Raja Sagara Dam</t>
+          <t>Leonardo da Vinci</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Charles Lindbergh</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Which city is known as the "Silicon Valley of India"?</t>
+          <t>Which was the first country to reach Mars orbit successfully?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Which country has the most volcanoes?</t>
+          <t>Which is the tallest building in the world?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Shanghai Tower</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Merdeka 118</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>One World Trade Center</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
     </row>
@@ -6102,11 +6102,11 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which country has the most nuclear weapons as of 2025?</t>
+          <t>Which is the largest country in the world by area?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
           <t>Russia</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>North Korea</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6137,31 +6137,31 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Which country has the largest economy (GDP)?</t>
+          <t>Which country has the highest number of Olympic medals overall?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
           <t>China</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Germany</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6172,176 +6172,176 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Which religion has the most followers in the world?</t>
+          <t>Which country has the longest coastline?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Islam</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Which country produces the most oil?</t>
+          <t>Which Indian monument has the highest number of tourist visits annually?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Red Fort</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Which country exports the most weapons?</t>
+          <t>Which was the first human-made object to reach space?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Which is the tallest statue in the world?</t>
+          <t>Which planet is closest to Earth most often?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Mercury</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which is the largest volcano in the world (by volume)?</t>
+          <t>Which is the first country to make education compulsory by law?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Mount Fuji</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Eyjafjallajökull</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mount Etna</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
@@ -6351,592 +6351,592 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which city has the most skyscrapers (over 150m)?</t>
+          <t>Which is the world’s first university?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Nalanda</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Takshashila</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Al-Qarawiyyin</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Takshashila</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which country has the highest number of billionaires?</t>
+          <t>Which is the first Indian city to get an underground metro?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Which mobile phone brand sells the most globally?</t>
+          <t>Which was the first country to use paper money?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Oppo</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Which is the most visited city in the world (tourism)?</t>
+          <t>Which country has the smallest population?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Which country has the most time zones (including territories)?</t>
+          <t>What was the first object sold on eBay?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Wristwatch</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Comic Book</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Which is the richest company in the world by market value (2025)?</t>
+          <t>Who was the first Indian Governor-General of independent India?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Lord Mountbatten</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Saudi Aramco</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Which country has the highest number of Olympic medals overall?</t>
+          <t>Which is the oldest dam in India still in use?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mettur Dam</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Krishna Raja Sagara Dam</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in India?</t>
+          <t>Which is the hottest planet in the solar system?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Venus</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Which is the most downloaded game of all time?</t>
+          <t>Which is the first country to launch a digital currency?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PUBG</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Candy Crush</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Minecraft</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>Bahamas</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Which is the busiest airport in the world by passenger volume?</t>
+          <t>What was the first video game ever created?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Beijing Capital</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Atlanta (ATL)</t>
+          <t>Pac-Man</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Heathrow</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dubai Intl</t>
+          <t>Tetris</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Atlanta (ATL)</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Which river carries the most water by volume?</t>
+          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>General V. K. Singh</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>General Manoj Pande</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Admiral Karambir Singh</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Which country has the most lakes?</t>
+          <t>Which Indian state was the first to achieve 100% literacy?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which animal is considered the fastest on land?</t>
+          <t>Which Indian city is known as the "first Smart City"?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Greyhound</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Which country has the highest literacy rate?</t>
+          <t>What is India’s first nuclear reactor called?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Dhruva</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>KAMINI</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Apsara</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>CIRUS</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Apsara</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Which is the most used currency in the world?</t>
+          <t>Which is the first Indian city to have a fully underground metro network?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Yen</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Pound Sterling</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Which is the largest bird in the world?</t>
+          <t>What was the first biosphere reserve in India?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Sundarbans</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Nilgiri</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Albatross</t>
+          <t>Nanda Devi</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Emu</t>
+          <t>Manas</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Nilgiri</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>Which was the first country to grant women the right to vote?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>

--- a/Data/WorldTop.xlsx
+++ b/Data/WorldTop.xlsx
@@ -467,561 +467,561 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which is the largest ocean in the world by area?</t>
+          <t>Which was the first car manufacturing company?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>Peugeot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Rolls-Royce</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Peugeot</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What was the first online shopping site?</t>
+          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Gangtok</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Gangtok</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which was the first Indian state formed on linguistic basis?</t>
+          <t>Which city is known as the "Silicon Valley of India"?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which is the largest island in the world?</t>
+          <t>Which country has the longest coastline?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>New Guinea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What was the first website ever created?</t>
+          <t>Which country produces the most oil?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Google.com</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wikipedia.org</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CERN.ch</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who was the first Indian female IPS officer?</t>
+          <t>Who was the first person to receive Bharat Ratna?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>S. Radhakrishnan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Anu Singh</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radhika Kumari</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pooja Thakur</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank to launch an ATM?</t>
+          <t>Which is the largest mammal in the world?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>African Elephant</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ICICI</t>
+          <t>Blue Whale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>Hippopotamus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Blue Whale</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Who was the first woman Prime Minister in the world?</t>
+          <t>Who was the first Indian in space?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Golda Meir</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which animal is considered the fastest on land?</t>
+          <t>Which is the world’s first programmable computer?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Colossus</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Z3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Greyhound</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Z3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which is the fastest bird in the world?</t>
+          <t>Who was India’s first female President?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Golden Eagle</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Swan</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which country has the most lakes?</t>
+          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Saina Nehwal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>P. V. Sindhu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Mary Kom</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which is the most downloaded app of all time?</t>
+          <t>Who was the first Prime Minister of India?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Sardar Patel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which is the world’s oldest living city?</t>
+          <t>Which is the tallest statue in the world?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which was the first car manufacturing company?</t>
+          <t>Which was the first animated feature film?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Cinderella</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Pinocchio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rolls-Royce</t>
+          <t>Bambi</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which is the smallest mammal by weight?</t>
+          <t>Who invented the first telephone?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pygmy Shrew</t>
+          <t>Alexander Graham Bell</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mouse Lemur</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pygmy Possum</t>
+          <t>Guglielmo Marconi</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>Alexander Graham Bell</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
+          <t>Which is the largest country in the world by area?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
@@ -1031,77 +1031,77 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which is the richest company in the world by market value (2025)?</t>
+          <t>Which is the first Indian city to have a fully underground metro network?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Saudi Aramco</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who invented the first electric light bulb?</t>
+          <t>Which is the coldest place on Earth?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>Siberia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Michael Faraday</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Vostok Station</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Vostok Station</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>Which country has the highest number of billionaires?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1121,1517 +1121,1517 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>What was the first country to recognize the United States as independent?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Morocco</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which country exports the most weapons?</t>
+          <t>Which was the first Indian company listed on NASDAQ?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Satyam</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Infosys</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which country has the largest forest area in the world?</t>
+          <t>Which was the first country to use paper money?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which is the world's first language (known oldest)?</t>
+          <t>Which is the largest state in India by area?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>Rajasthan</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in India?</t>
+          <t>Who was the first female Prime Minister of India?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which is the world’s first country to ban tobacco completely?</t>
+          <t>Who was the first woman to fly solo around the world?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Valentina Tereshkova</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Anne Morrow</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which bird is believed to be extinct due to human activity?</t>
+          <t>Which Indian city is known as the 'City of Lakes'?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Penguin</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bald Eagle</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>Udaipur</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What was the first cloned mammal?</t>
+          <t>Which bird is believed to be extinct due to human activity?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Molly the Cow</t>
+          <t>Penguin</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Polly the Pig</t>
+          <t>Bald Eagle</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>Dodo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kitty the Cat</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>Dodo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which is the deepest ocean in the world?</t>
+          <t>Which is the world's first language (known oldest)?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Sumerian</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Sumerian</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Who was the first person to go to space?</t>
+          <t>Which Indian monument has the highest number of tourist visits annually?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Red Fort</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which is the smallest country in the world by land area?</t>
+          <t>Which was the first Indian film to win an Oscar?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Slumdog Millionaire</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Gandhi</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What was the first country to recognize the United States as independent?</t>
+          <t>Who was the first Indian woman in space?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Ritu Karidhal</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Who was the first woman ruler of India?</t>
+          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rani Lakshmibai</t>
+          <t>IIT Delhi</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>IIT Bombay</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ahilyabai Holkar</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>IIT Madras</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which country produces the most oil?</t>
+          <t>Which is the largest freshwater lake in the world by surface area?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Lake Victoria</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Lake Superior</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which is the highest waterfall in the world?</t>
+          <t>Which is the largest mosque in India?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Niagara Falls</t>
+          <t>Jama Masjid, Delhi</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tugela Falls</t>
+          <t>Mecca Masjid, Hyderabad</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yosemite Falls</t>
+          <t>Nakhoda Masjid, Kolkata</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which was the first Indian company listed on NASDAQ?</t>
+          <t>Which Indian state was the first to achieve 100% literacy?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Satyam</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
+          <t>Who was the first President of the world’s first republic (USA)?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>George Washington</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dorothy Hodgkin</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lise Meitner</t>
+          <t>John Adams</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>George Washington</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who was the first woman to win a Nobel Prize?</t>
+          <t>Who was the first human in space?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Rosalind Franklin</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which is the first Indian mission to Mars?</t>
+          <t>Which is the deepest ocean in the world?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>IRNSS</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which was the first country to legalize same-sex marriage?</t>
+          <t>Which was the first messaging app?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>ICQ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>AIM</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>ICQ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who was the first Indian Miss World?</t>
+          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sushmita Sen</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lara Dutta</t>
+          <t>Neeraj Chopra</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>Hima Das</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aishwarya Rai</t>
+          <t>Anju George</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which city is known as the "Silicon Valley of India"?</t>
+          <t>Which is the fastest bird in the world?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Golden Eagle</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Swan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who is the first Indian to climb Mount Everest?</t>
+          <t>What was the world’s first printed book?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bachendri Pal</t>
+          <t>The Holy Bible</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tenzing Norgay</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Santosh Yadav</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>Quran</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which was the first Indian communication satellite?</t>
+          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Sunil Gavaskar</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>APPLESAT</t>
+          <t>Sachin Tendulkar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>INSAT-2A</t>
+          <t>Rahul Dravid</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which is the largest continent by land area?</t>
+          <t>Which is the world’s oldest living city?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Varanasi</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which is the longest river in the world?</t>
+          <t>Which Indian river has the largest length within India?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>Brahmaputra</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>Ganga</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Nile</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the 'City of Lakes'?</t>
+          <t>What was the first email ever sent?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Login123</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Indian river got the status of ‘living entity’ first?</t>
+          <t>Which is the first country to launch a digital currency?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Bahamas</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which was the first Indian city to be electrified?</t>
+          <t>Who invented the first electric light bulb?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Michael Faraday</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which was the world's first artificial satellite?</t>
+          <t>Which is the largest dam in India by volume?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apollo 11</t>
+          <t>Sardar Sarovar Dam</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Bhakra Nangal</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luna 2</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which country has the most nuclear weapons as of 2025?</t>
+          <t>Which is the smallest bird in the world?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Hummingbird</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Parakeet</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>Finch</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Hummingbird</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which is the smallest state in India by area?</t>
+          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Amartya Sen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which is the largest freshwater lake in the world by surface area?</t>
+          <t>Which is the smallest state in India by area?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lake Victoria</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Goa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which was the first movie with sound (talkie)?</t>
+          <t>Which Indian state launched the first electric vehicle policy?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>King Kong</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>Karnataka</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which was the first city to host the modern Olympic Games?</t>
+          <t>Which is the first country to make education compulsory by law?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which country has the largest economy (GDP)?</t>
+          <t>What was the first successful vaccine developed for?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Smallpox</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Smallpox</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which was the first Indian movie submitted for the Oscars?</t>
+          <t>Who was the first person to go to space?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Who was the first woman to fly solo around the world?</t>
+          <t>Which is the world's first man-made nuclear reactor?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Fermi-1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Valentina Tereshkova</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>DIDO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anne Morrow</t>
+          <t>THTR-300</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
+          <t>Which country has the highest GDP in the world?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IIT Delhi</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>IIT Bombay</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>IIT Madras</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Who was the first female Prime Minister of India?</t>
+          <t>Who was the first Indian Miss World?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Sushmita Sen</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>Lara Dutta</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Reita Faria</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Aishwarya Rai</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Reita Faria</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which was the first Indian satellite to orbit the Moon?</t>
+          <t>Which Indian state has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Indian state has the highest literacy rate?</t>
+          <t>Which is the first Indian city to have a monorail?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Mumbai</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which is the smallest bone in the human body?</t>
+          <t>Which country has the highest population in the world?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Femur</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tibia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ulna</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>India</t>
         </is>
       </c>
     </row>
@@ -2641,1327 +2641,1327 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which planet has the most moons?</t>
+          <t>Which is the first Indian bank?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Allahabad Bank</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which is the longest railway platform in the world?</t>
+          <t>Which country has the most lakes?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gorakhpur</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kharagpur</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Who was the first Indian in space?</t>
+          <t>Which is the first country to adopt a national flag?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which was the first Indian film to win an Oscar?</t>
+          <t>What is the name of India’s first satellite?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Slumdog Millionaire</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Chandrayaan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Aryabhata</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Indian river has the largest length within India?</t>
+          <t>Which is the most populated city in the world?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brahmaputra</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Tokyo</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which country has the most time zones (including territories)?</t>
+          <t>Which is the tallest animal in the world?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Camel</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Moose</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Giraffe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which country has the highest GDP in the world?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>China</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Who invented the first telephone?</t>
+          <t>Who was the first woman ruler of India?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Rani Lakshmibai</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>Ahilyabai Holkar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guglielmo Marconi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which was the first programming language?</t>
+          <t>Which was the first city to host the modern Olympic Games?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>COBOL</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Who was India’s first female President?</t>
+          <t>Which is the oldest dam in India still in use?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Mettur Dam</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Krishna Raja Sagara Dam</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Who was the first President of the world’s first republic (USA)?</t>
+          <t>Which was the first Indian state formed on linguistic basis?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>John Adams</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which is the largest state in India by area?</t>
+          <t>Who was the first woman Prime Minister in the world?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Golda Meir</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
+          <t>What was the first object sold on eBay?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Wristwatch</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Amartya Sen</t>
+          <t>Comic Book</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Who was the first person to step on the Moon?</t>
+          <t>Which country has the largest number of active military personnel?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Michael Collins</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which is the largest dam in India by volume?</t>
+          <t>Which Indian state was the first to implement the GST?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sardar Sarovar Dam</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bhakra Nangal</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Assam</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which country has the highest number of billionaires?</t>
+          <t>What was the name of the first computer virus?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>ILOVEYOU</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Creeper</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Stuxnet</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>WannaCry</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Creeper</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which is the world’s first democracy?</t>
+          <t>Which country has the largest economy (GDP)?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Athens</t>
-        </is>
-      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What was the world's first message sent over the internet?</t>
+          <t>Which is the world’s first country to ban tobacco completely?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>Bhutan</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which is the highest mountain peak in the world?</t>
+          <t>What was the first computer called?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>IBM 1401</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Makalu</t>
+          <t>Apple I</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>ENIAC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in the world?</t>
+          <t>Who invented the first airplane?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Leonardo da Vinci</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Charles Lindbergh</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which Indian state hosted the first International G20 summit in India?</t>
+          <t>Who was the first woman to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Rosalind Franklin</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Who was the first human in space?</t>
+          <t>Which is the most downloaded game of all time?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>PUBG</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Candy Crush</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Minecraft</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which Indian state launched the first electric vehicle policy?</t>
+          <t>Which is the first country to implement a constitution?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of the United Kingdom?</t>
+          <t>Which is the largest species of shark?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
+          <t>Tiger Shark</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>Hammerhead Shark</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>Whale Shark</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tony Blair</t>
+          <t>Great White Shark</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>Whale Shark</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which is the world's most visited heritage site?</t>
+          <t>Which planet is closest to Earth most often?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Eiffel Tower</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Colosseum</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>Mercury</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which is the tallest statue in the world?</t>
+          <t>Which is the largest bird in the world?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Emu</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Ostrich</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a monorail?</t>
+          <t>Who was the first Indian to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>C.V. Raman</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which is the smallest bird in the world?</t>
+          <t>Which Indian airport is the busiest by passenger traffic?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Parakeet</t>
+          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Kempegowda Intl (Bangalore)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Finch</t>
+          <t>Rajiv Gandhi Intl (Hyderabad)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which is the most populated city in the world?</t>
+          <t>What is the world’s tallest statue as of 2025?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which is the world's first man-made nuclear reactor?</t>
+          <t>Which is the largest desert in the world?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fermi-1</t>
+          <t>Sahara</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>Gobi</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>DIDO</t>
+          <t>Kalahari</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>THTR-300</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which is the deepest lake in the world?</t>
+          <t>Which is the world's most visited heritage site?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>Eiffel Tower</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Colosseum</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Caspian Sea</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which religion has the most followers in the world?</t>
+          <t>What was the first video game ever created?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Islam</t>
+          <t>Pac-Man</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Tetris</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What was the name of the first computer virus?</t>
+          <t>Which was the first Indian film?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ILOVEYOU</t>
+          <t>Alam Ara</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stuxnet</t>
+          <t>Sholay</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>WannaCry</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which city has the most skyscrapers (over 150m)?</t>
+          <t>Which country exports the most weapons?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which is the longest national highway in India?</t>
+          <t>Which Indian was the first to win an Olympic gold medal?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NH7</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>NH27</t>
+          <t>Major Dhyan Chand</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NH19</t>
+          <t>KD Jadhav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which is the tallest animal in the world?</t>
+          <t>Who is the first Indian to climb Mount Everest?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Bachendri Pal</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Tenzing Norgay</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Camel</t>
+          <t>Santosh Yadav</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Moose</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What was the world’s first printed book?</t>
+          <t>Which country launched the world's first satellite?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>The Holy Bible</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Quran</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
+          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Titanic</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>General V. K. Singh</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Avengers: Endgame</t>
+          <t>General Manoj Pande</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Oppenheimer</t>
+          <t>Admiral Karambir Singh</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
     </row>
@@ -3971,172 +3971,172 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which is the most visited city in the world (tourism)?</t>
+          <t>Which was the first programming language?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>COBOL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Fortran</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Assembly</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Fortran</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which mobile phone brand sells the most globally?</t>
+          <t>Which is the most spoken language in the world?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Oppo</t>
+          <t>Mandarin</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>What was the first computer called?</t>
+          <t>Which country has the most nuclear weapons as of 2025?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IBM 1401</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Apple I</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which river carries the most water by volume?</t>
+          <t>Which country has the largest forest area in the world?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which Indian airport is the busiest by passenger traffic?</t>
+          <t>Which is the world's first novel ever written?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>Don Quixote</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kempegowda Intl (Bangalore)</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi Intl (Hyderabad)</t>
+          <t>Beowulf</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
     </row>
@@ -4146,487 +4146,487 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Who was the first person to win two Nobel Prizes?</t>
+          <t>Who was the first Indian female IPS officer?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Albert Einstein</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Anu Singh</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Linus Pauling</t>
+          <t>Radhika Kumari</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Erwin Schrödinger</t>
+          <t>Pooja Thakur</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which is the largest bird in the world?</t>
+          <t>Which city has the most skyscrapers (over 150m)?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Albatross</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Emu</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Hong Kong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which was the first Indian express train?</t>
+          <t>Which is the world’s first democracy?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Shatabdi Express</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Rajdhani Express</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Duronto Express</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which country has the highest population in the world?</t>
+          <t>Which is India’s first supercomputer?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Shakti</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Virgo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Mihir</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Which country launched the world's first satellite?</t>
+          <t>Which was the first Indian express train?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Shatabdi Express</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Rajdhani Express</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Duronto Express</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>What is the world’s tallest statue as of 2025?</t>
+          <t>Which is the largest island in the world?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>New Guinea</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Greenland</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which was the first messaging app?</t>
+          <t>Which is the deepest lake in the world?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AIM</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Caspian Sea</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which is the first country to adopt a national flag?</t>
+          <t>Which animal is considered the fastest on land?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Greyhound</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cheetah</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
+          <t>Which is the most spoken language in India?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Saina Nehwal</t>
+          <t>English</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P. V. Sindhu</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mary Kom</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>Hindi</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which is the first Indian state to ban plastic completely?</t>
+          <t>Which is the busiest airport in the world by passenger volume?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Beijing Capital</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Atlanta (ATL)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Heathrow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Dubai Intl</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Atlanta (ATL)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which Indian was the first to win an Olympic gold medal?</t>
+          <t>What is India’s first nuclear reactor called?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>Dhruva</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>KAMINI</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Major Dhyan Chand</t>
+          <t>Apsara</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>KD Jadhav</t>
+          <t>CIRUS</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>Apsara</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a Nobel Prize?</t>
+          <t>Which is the largest volcano in the world (by volume)?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Mount Fuji</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>C.V. Raman</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Eyjafjallajökull</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Mount Etna</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which country is the largest producer of gold?</t>
+          <t>Which mobile phone brand sells the most globally?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Oppo</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which Indian city is the first to use electric buses at scale?</t>
+          <t>What was the world’s first search engine?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Archie</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>AltaVista</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Archie</t>
         </is>
       </c>
     </row>
@@ -4667,71 +4667,71 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which country has the most volcanoes?</t>
+          <t>Which country has the most time zones (including territories)?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank?</t>
+          <t>Which was the first country to legalize same-sex marriage?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Allahabad Bank</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>Netherlands</t>
         </is>
       </c>
     </row>
@@ -4741,977 +4741,977 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>What was the first email ever sent?</t>
+          <t>Who was the first President of India?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>Dr. S. Radhakrishnan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Login123</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which country has the largest number of active military personnel?</t>
+          <t>Who was the first Prime Minister of the United Kingdom?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Winston Churchill</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tony Blair</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which is the largest species of shark?</t>
+          <t>Which is the smallest mammal by weight?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tiger Shark</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Hammerhead Shark</t>
+          <t>Pygmy Shrew</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>Mouse Lemur</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Great White Shark</t>
+          <t>Pygmy Possum</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of India?</t>
+          <t>Which language has the most native speakers in the world?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sardar Patel</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Mandarin Chinese</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Mandarin Chinese</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which is the first country to implement a constitution?</t>
+          <t>Which was the first human-made object to reach space?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman in space?</t>
+          <t>Which is the first Indian state to ban plastic completely?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ritu Karidhal</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Sikkim</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which is India’s first supercomputer?</t>
+          <t>Which country has the highest number of Olympic medals overall?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Shakti</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Virgo</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mihir</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Which was the first animated feature film?</t>
+          <t>Which is the smallest continent by land area?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cinderella</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pinocchio</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bambi</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Which is the most used currency in the world?</t>
+          <t>What was the first cloned mammal?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Molly the Cow</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Yen</t>
+          <t>Polly the Pig</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pound Sterling</t>
+          <t>Kitty the Cat</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Which is India’s first indigenously built aircraft carrier?</t>
+          <t>Which is the first Indian mission to Mars?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>INS Viraat</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>INS Arihant</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>INS Trikand</t>
+          <t>IRNSS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Who was the first person to receive Bharat Ratna?</t>
+          <t>What was the first smartphone ever made?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>S. Radhakrishnan</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>IBM Simon</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Nokia 3310</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Motorola DynaTAC</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>IBM Simon</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Which is the largest mosque in India?</t>
+          <t>Which is the longest river in the world?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jama Masjid, Delhi</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mecca Masjid, Hyderabad</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nakhoda Masjid, Kolkata</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>Nile</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>What was the first successful vaccine developed for?</t>
+          <t>Which is the highest waterfall in the world?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Niagara Falls</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Tugela Falls</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Angel Falls</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>Yosemite Falls</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>Angel Falls</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
+          <t>Which was the first Indian movie submitted for the Oscars?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sunil Gavaskar</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sachin Tendulkar</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rahul Dravid</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Mother India</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
+          <t>Which Indian city is the first to use electric buses at scale?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Neeraj Chopra</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Hima Das</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Anju George</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>Pune</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to implement the GST?</t>
+          <t>Which was the first Indian city to be electrified?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Darjeeling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Darjeeling</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which is the first artificial satellite sent into space?</t>
+          <t>Which is the most used currency in the world?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Vostok</t>
+          <t>Yen</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>US Dollar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Pound Sterling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>US Dollar</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Which is the busiest airport in the world by passenger volume?</t>
+          <t>What was the first online shopping site?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Beijing Capital</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Atlanta (ATL)</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Heathrow</t>
+          <t>NetMarket</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dubai Intl</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Atlanta (ATL)</t>
+          <t>NetMarket</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which is the largest volcano in the world (by volume)?</t>
+          <t>Which is the first artificial satellite sent into space?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mount Fuji</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>Vostok</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Eyjafjallajökull</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mount Etna</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which was the first war of Indian independence?</t>
+          <t>Which is the first Indian bank to launch an ATM?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Battle of Plassey</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Battle of Panipat</t>
+          <t>ICICI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>HSBC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which is the largest mammal in the world?</t>
+          <t>Which was the first Indian communication satellite?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>African Elephant</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>APPLESAT</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hippopotamus</t>
+          <t>INSAT-2A</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Which is the smallest continent by land area?</t>
+          <t>Which is the highest mountain peak in the world?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Makalu</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Mount Everest</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Who was the first President of India?</t>
+          <t>Which is the longest national highway in India?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>NH44</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>NH7</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Dr. S. Radhakrishnan</t>
+          <t>NH27</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>NH19</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>NH44</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Which was the first Indian film?</t>
+          <t>Which planet has the most moons?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Alam Ara</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sholay</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Saturn</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>What is the name of India’s first satellite?</t>
+          <t>Who was the first person to win two Nobel Prizes?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Albert Einstein</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Linus Pauling</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Chandrayaan</t>
+          <t>Erwin Schrödinger</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>What was the first ever video uploaded to YouTube?</t>
+          <t>Which was the first movie with sound (talkie)?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>King Kong</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Hello World</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Test Video</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Launch Video</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which is the world's first novel ever written?</t>
+          <t>Who was the first Indian Governor-General of independent India?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Don Quixote</t>
+          <t>Lord Mountbatten</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Beowulf</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Which is the most downloaded game of all time?</t>
+          <t>Which is the smallest country in the world by land area?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PUBG</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Candy Crush</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Minecraft</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
@@ -5721,627 +5721,627 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>What was the world’s first search engine?</t>
+          <t>Which was the first country to reach Mars orbit successfully?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AltaVista</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Which was the first nation to reach the South Pole?</t>
+          <t>What was the first biosphere reserve in India?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sundarbans</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Nilgiri</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Nanda Devi</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Manas</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Nilgiri</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Which is the largest desert in the world?</t>
+          <t>Which was the first war of Indian independence?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Sahara</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Gobi</t>
+          <t>Battle of Plassey</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Kalahari</t>
+          <t>Battle of Panipat</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Which is the coldest place on Earth?</t>
+          <t>Which Indian state hosted the first International G20 summit in India?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Siberia</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Which is the world’s first programmable computer?</t>
+          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Colossus</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>Dorothy Hodgkin</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>Lise Meitner</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which country has the highest literacy rate?</t>
+          <t>Which is the richest company in the world by market value (2025)?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>What was the first smartphone ever made?</t>
+          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>Titanic</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>Avatar</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Nokia 3310</t>
+          <t>Avengers: Endgame</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Motorola DynaTAC</t>
+          <t>Oppenheimer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>Avatar</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Who invented the first airplane?</t>
+          <t>Who was the first person to step on the Moon?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Charles Lindbergh</t>
+          <t>Michael Collins</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Which was the first country to reach Mars orbit successfully?</t>
+          <t>Which is India’s first indigenously built aircraft carrier?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INS Viraat</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>INS Arihant</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>INS Trikand</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Which is the tallest building in the world?</t>
+          <t>Which is the largest ocean in the world by area?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Shanghai Tower</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Merdeka 118</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>One World Trade Center</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which language has the most native speakers in the world?</t>
+          <t>What was the first ever video uploaded to YouTube?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Hello World</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Mandarin Chinese</t>
+          <t>Test Video</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Launch Video</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Mandarin Chinese</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which is the largest country in the world by area?</t>
+          <t>Which religion has the most followers in the world?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Christianity</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Islam</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Christianity</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Which country has the highest number of Olympic medals overall?</t>
+          <t>What was the world's first message sent over the internet?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>LO</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>LO</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Which country has the longest coastline?</t>
+          <t>Which is the longest railway platform in the world?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Gorakhpur</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Kharagpur</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hubballi</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Howrah</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hubballi</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Which Indian monument has the highest number of tourist visits annually?</t>
+          <t>Which country has the most volcanoes?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Red Fort</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Which was the first human-made object to reach space?</t>
+          <t>Which Indian city is known as the "first Smart City"?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Which planet is closest to Earth most often?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which is the first country to make education compulsory by law?</t>
+          <t>Which river carries the most water by volume?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
@@ -6351,487 +6351,487 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which is the world’s first university?</t>
+          <t>What was the first website ever created?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Nalanda</t>
+          <t>Google.com</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>Wikipedia.org</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>CERN.ch</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al-Qarawiyyin</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to get an underground metro?</t>
+          <t>Which Indian river got the status of ‘living entity’ first?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Ganga</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Which was the first country to use paper money?</t>
+          <t>Which is the world’s first university?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Nalanda</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Takshashila</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Al-Qarawiyyin</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Takshashila</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Which country has the smallest population?</t>
+          <t>Which was the first nation to reach the South Pole?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Norway</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>What was the first object sold on eBay?</t>
+          <t>Which was the first Indian satellite to orbit the Moon?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wristwatch</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Comic Book</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Who was the first Indian Governor-General of independent India?</t>
+          <t>Which is the most downloaded app of all time?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Lord Mountbatten</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Which is the oldest dam in India still in use?</t>
+          <t>Which is the tallest building in the world?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Mettur Dam</t>
+          <t>Shanghai Tower</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Krishna Raja Sagara Dam</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Merdeka 118</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>One World Trade Center</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Which is the hottest planet in the solar system?</t>
+          <t>Which is the first Indian city to get an underground metro?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Which is the first country to launch a digital currency?</t>
+          <t>Which is the hottest planet in the solar system?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Venus</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>What was the first video game ever created?</t>
+          <t>Which is the most visited city in the world (tourism)?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Pac-Man</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tetris</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Paris</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
+          <t>Which country has the smallest population?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>General V. K. Singh</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>General Manoj Pande</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Admiral Karambir Singh</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to achieve 100% literacy?</t>
+          <t>Which is the largest continent by land area?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the "first Smart City"?</t>
+          <t>Which country has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Andorra</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>What is India’s first nuclear reactor called?</t>
+          <t>Which country is the largest producer of gold?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Dhruva</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>KAMINI</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CIRUS</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -6841,102 +6841,102 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a fully underground metro network?</t>
+          <t>Which is the smallest bone in the human body?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Femur</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Tibia</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Stapes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Ulna</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Stapes</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>What was the first biosphere reserve in India?</t>
+          <t>Which was the first country to grant women the right to vote?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Sundarbans</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Nanda Devi</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Manas</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which was the first country to grant women the right to vote?</t>
+          <t>Which was the world's first artificial satellite?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Apollo 11</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Luna 2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>

--- a/Data/WorldTop.xlsx
+++ b/Data/WorldTop.xlsx
@@ -471,732 +471,732 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which was the first car manufacturing company?</t>
+          <t>Which Indian state hosted the first International G20 summit in India?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rolls-Royce</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
+          <t>Who invented the first telephone?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Alexander Graham Bell</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Guglielmo Marconi</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Alexander Graham Bell</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which city is known as the "Silicon Valley of India"?</t>
+          <t>Which country has the highest number of Olympic medals overall?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which country has the longest coastline?</t>
+          <t>Which is the world's first novel ever written?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Don Quixote</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Beowulf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which country produces the most oil?</t>
+          <t>Which bird is believed to be extinct due to human activity?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Penguin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Bald Eagle</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Dodo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Dodo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who was the first person to receive Bharat Ratna?</t>
+          <t>Which was the first Indian state formed on linguistic basis?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S. Radhakrishnan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which is the largest mammal in the world?</t>
+          <t>Which is the first country to launch a digital currency?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>African Elephant</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hippopotamus</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>Bahamas</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Who was the first Indian in space?</t>
+          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Sunil Gavaskar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>Sachin Tendulkar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>Rahul Dravid</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which is the world’s first programmable computer?</t>
+          <t>Who is the first Indian to climb Mount Everest?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>Bachendri Pal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Colossus</t>
+          <t>Tenzing Norgay</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>Santosh Yadav</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Who was India’s first female President?</t>
+          <t>Which country has the highest number of billionaires?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
+          <t>What was the first website ever created?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>Google.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Saina Nehwal</t>
+          <t>Wikipedia.org</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P. V. Sindhu</t>
+          <t>CERN.ch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mary Kom</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of India?</t>
+          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Titanic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sardar Patel</t>
+          <t>Avatar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Avengers: Endgame</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Oppenheimer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Avatar</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which is the tallest statue in the world?</t>
+          <t>Which is the largest country in the world by area?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which was the first animated feature film?</t>
+          <t>Which is the largest mosque in India?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Jama Masjid, Delhi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cinderella</t>
+          <t>Mecca Masjid, Hyderabad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pinocchio</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bambi</t>
+          <t>Nakhoda Masjid, Kolkata</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who invented the first telephone?</t>
+          <t>Which is the tallest statue in the world?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guglielmo Marconi</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which is the largest country in the world by area?</t>
+          <t>Which planet has the most moons?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Saturn</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a fully underground metro network?</t>
+          <t>Which is the most used currency in the world?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Yen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>US Dollar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Pound Sterling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>US Dollar</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which is the coldest place on Earth?</t>
+          <t>Which was the first car manufacturing company?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Siberia</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Peugeot</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Rolls-Royce</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Peugeot</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which country has the highest number of billionaires?</t>
+          <t>Which was the first country to reach Mars orbit successfully?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What was the first country to recognize the United States as independent?</t>
+          <t>Which is the deepest lake in the world?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Caspian Sea</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which was the first Indian company listed on NASDAQ?</t>
+          <t>Which is the tallest building in the world?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Shanghai Tower</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Merdeka 118</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Satyam</t>
+          <t>One World Trade Center</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
     </row>
@@ -1206,2132 +1206,2132 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which was the first country to use paper money?</t>
+          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IIT Delhi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>IIT Bombay</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>IIT Madras</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which is the largest state in India by area?</t>
+          <t>Which is the first Indian bank?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Allahabad Bank</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who was the first female Prime Minister of India?</t>
+          <t>Which is the world’s oldest living city?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Varanasi</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Who was the first woman to fly solo around the world?</t>
+          <t>Which is the largest ocean in the world by area?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Valentina Tereshkova</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anne Morrow</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the 'City of Lakes'?</t>
+          <t>Which is the largest dam in India by volume?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Sardar Sarovar Dam</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Bhakra Nangal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which bird is believed to be extinct due to human activity?</t>
+          <t>Which language has the most native speakers in the world?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Penguin</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bald Eagle</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>Mandarin Chinese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>Mandarin Chinese</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which is the world's first language (known oldest)?</t>
+          <t>Who was the first person to receive Bharat Ratna?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>S. Radhakrishnan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which Indian monument has the highest number of tourist visits annually?</t>
+          <t>Which is the world’s first university?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Nalanda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Red Fort</t>
+          <t>Takshashila</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Al-Qarawiyyin</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Takshashila</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which was the first Indian film to win an Oscar?</t>
+          <t>Who was the first Indian Miss World?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Sushmita Sen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>Lara Dutta</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Slumdog Millionaire</t>
+          <t>Reita Faria</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Aishwarya Rai</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Reita Faria</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman in space?</t>
+          <t>What was the first successful vaccine developed for?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ritu Karidhal</t>
+          <t>Smallpox</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Smallpox</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
+          <t>Which is the highest mountain peak in the world?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IIT Delhi</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IIT Bombay</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IIT Madras</t>
+          <t>Makalu</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>Mount Everest</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which is the largest freshwater lake in the world by surface area?</t>
+          <t>Who was the first Indian woman in space?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lake Victoria</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>Ritu Karidhal</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which is the largest mosque in India?</t>
+          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jama Masjid, Delhi</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mecca Masjid, Hyderabad</t>
+          <t>Saina Nehwal</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>P. V. Sindhu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nakhoda Masjid, Kolkata</t>
+          <t>Mary Kom</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to achieve 100% literacy?</t>
+          <t>Which is the deepest ocean in the world?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who was the first President of the world’s first republic (USA)?</t>
+          <t>Which is India’s first supercomputer?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Shakti</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>Virgo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>John Adams</t>
+          <t>Mihir</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who was the first human in space?</t>
+          <t>What was the first country to recognize the United States as independent?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Morocco</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which is the deepest ocean in the world?</t>
+          <t>Which is the smallest mammal by weight?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>Pygmy Shrew</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>Mouse Lemur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Pygmy Possum</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which was the first messaging app?</t>
+          <t>Which is the first Indian bank to launch an ATM?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AIM</t>
+          <t>ICICI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>HSBC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
+          <t>Which Indian state was the first to implement the GST?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Neeraj Chopra</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hima Das</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anju George</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>Assam</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which is the fastest bird in the world?</t>
+          <t>What was the first ever video uploaded to YouTube?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Golden Eagle</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Hello World</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>Test Video</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Swan</t>
+          <t>Launch Video</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What was the world’s first printed book?</t>
+          <t>Which is the first Indian city to get an underground metro?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>The Holy Bible</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Quran</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
+          <t>Which is the largest state in India by area?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sunil Gavaskar</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sachin Tendulkar</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rahul Dravid</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Rajasthan</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which is the world’s oldest living city?</t>
+          <t>Which was the first country to legalize same-sex marriage?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Netherlands</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Indian river has the largest length within India?</t>
+          <t>Which country has the most lakes?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brahmaputra</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What was the first email ever sent?</t>
+          <t>Which was the first Indian satellite to orbit the Moon?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Login123</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which is the first country to launch a digital currency?</t>
+          <t>Which Indian state launched the first electric vehicle policy?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Karnataka</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Who invented the first electric light bulb?</t>
+          <t>Which was the first country to use paper money?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Michael Faraday</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which is the largest dam in India by volume?</t>
+          <t>Who was the first person to step on the Moon?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sardar Sarovar Dam</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bhakra Nangal</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Michael Collins</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which is the smallest bird in the world?</t>
+          <t>Which is the smallest continent by land area?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Parakeet</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Finch</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
+          <t>Which was the first messaging app?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>ICQ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Amartya Sen</t>
+          <t>AIM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>ICQ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which is the smallest state in India by area?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Indian state launched the first electric vehicle policy?</t>
+          <t>Which is the first country to implement a constitution?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which is the first country to make education compulsory by law?</t>
+          <t>Which is the most downloaded game of all time?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>PUBG</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Candy Crush</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Minecraft</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What was the first successful vaccine developed for?</t>
+          <t>Which Indian state was the first to achieve 100% literacy?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Who was the first person to go to space?</t>
+          <t>Which is the largest island in the world?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>New Guinea</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Greenland</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which is the world's first man-made nuclear reactor?</t>
+          <t>Which was the first animated feature film?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fermi-1</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>Cinderella</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DIDO</t>
+          <t>Pinocchio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>THTR-300</t>
+          <t>Bambi</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which country has the highest GDP in the world?</t>
+          <t>Who was the first Prime Minister of India?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Sardar Patel</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Who was the first Indian Miss World?</t>
+          <t>Which is the first country to make education compulsory by law?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sushmita Sen</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lara Dutta</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aishwarya Rai</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which Indian state has the highest literacy rate?</t>
+          <t>Which Indian river has the largest length within India?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Brahmaputra</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Ganga</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a monorail?</t>
+          <t>Which is the world's first language (known oldest)?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Sumerian</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Sumerian</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which country has the highest population in the world?</t>
+          <t>What was the world's first message sent over the internet?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>LO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>LO</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank?</t>
+          <t>Which country has the highest GDP in the world?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Allahabad Bank</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which country has the most lakes?</t>
+          <t>Who was the first woman ruler of India?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Rani Lakshmibai</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ahilyabai Holkar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which is the first country to adopt a national flag?</t>
+          <t>Who was India’s first female President?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What is the name of India’s first satellite?</t>
+          <t>Which is the oldest dam in India still in use?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Mettur Dam</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Krishna Raja Sagara Dam</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chandrayaan</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which is the most populated city in the world?</t>
+          <t>Which country has the smallest population?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which is the tallest animal in the world?</t>
+          <t>Which is the hottest planet in the solar system?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Camel</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Moose</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Venus</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>Which Indian airport is the busiest by passenger traffic?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kempegowda Intl (Bangalore)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rajiv Gandhi Intl (Hyderabad)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Who was the first woman ruler of India?</t>
+          <t>Who was the first human in space?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rani Lakshmibai</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ahilyabai Holkar</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which was the first city to host the modern Olympic Games?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which is the oldest dam in India still in use?</t>
+          <t>Which Indian city is the first to use electric buses at scale?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mettur Dam</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Krishna Raja Sagara Dam</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Pune</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which was the first Indian state formed on linguistic basis?</t>
+          <t>Which Indian was the first to win an Olympic gold medal?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Major Dhyan Chand</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>KD Jadhav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Who was the first woman Prime Minister in the world?</t>
+          <t>Which was the first country to grant women the right to vote?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Golda Meir</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What was the first object sold on eBay?</t>
+          <t>Which Indian state has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wristwatch</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Comic Book</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which country has the largest number of active military personnel?</t>
+          <t>Which is the largest continent by land area?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to implement the GST?</t>
+          <t>Which is the richest company in the world by market value (2025)?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What was the name of the first computer virus?</t>
+          <t>Which is the world’s first democracy?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ILOVEYOU</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Stuxnet</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>WannaCry</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which country has the largest economy (GDP)?</t>
+          <t>Who was the first person to go to space?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which is the world’s first country to ban tobacco completely?</t>
+          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Neeraj Chopra</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Hima Das</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Anju George</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What was the first computer called?</t>
+          <t>Which country launched the world's first satellite?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IBM 1401</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Apple I</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Who invented the first airplane?</t>
+          <t>What was the first object sold on eBay?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>Wristwatch</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Comic Book</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Charles Lindbergh</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
     </row>
@@ -3341,767 +3341,767 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Who was the first woman to win a Nobel Prize?</t>
+          <t>Which country produces the most oil?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Rosalind Franklin</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which is the most downloaded game of all time?</t>
+          <t>Who invented the first airplane?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PUBG</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Candy Crush</t>
+          <t>Leonardo da Vinci</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Minecraft</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>Charles Lindbergh</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which is the first country to implement a constitution?</t>
+          <t>What is the world’s tallest statue as of 2025?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which is the largest species of shark?</t>
+          <t>Which is the longest river in the world?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tiger Shark</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Hammerhead Shark</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Great White Shark</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>Nile</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which planet is closest to Earth most often?</t>
+          <t>Which is the first artificial satellite sent into space?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Vostok</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which is the largest bird in the world?</t>
+          <t>What was the name of the first computer virus?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>ILOVEYOU</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Creeper</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Albatross</t>
+          <t>Stuxnet</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emu</t>
+          <t>WannaCry</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Creeper</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a Nobel Prize?</t>
+          <t>What was the world’s first printed book?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>The Holy Bible</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>C.V. Raman</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Quran</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which Indian airport is the busiest by passenger traffic?</t>
+          <t>Which country has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kempegowda Intl (Bangalore)</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi Intl (Hyderabad)</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>Andorra</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What is the world’s tallest statue as of 2025?</t>
+          <t>Who was the first woman to fly solo around the world?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Valentina Tereshkova</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Anne Morrow</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which is the largest desert in the world?</t>
+          <t>Who invented the first electric light bulb?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sahara</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Gobi</t>
+          <t>Michael Faraday</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kalahari</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which is the world's most visited heritage site?</t>
+          <t>Which country has the longest coastline?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Eiffel Tower</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colosseum</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What was the first video game ever created?</t>
+          <t>Which was the first city to host the modern Olympic Games?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Pac-Man</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tetris</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which was the first Indian film?</t>
+          <t>Which is the largest volcano in the world (by volume)?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Alam Ara</t>
+          <t>Mount Fuji</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sholay</t>
+          <t>Eyjafjallajökull</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>Mount Etna</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which country exports the most weapons?</t>
+          <t>Which is the fastest bird in the world?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Golden Eagle</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Swan</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which Indian was the first to win an Olympic gold medal?</t>
+          <t>Which is the largest mammal in the world?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>African Elephant</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Major Dhyan Chand</t>
+          <t>Blue Whale</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KD Jadhav</t>
+          <t>Hippopotamus</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>Blue Whale</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Who is the first Indian to climb Mount Everest?</t>
+          <t>Which was the first Indian film to win an Oscar?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bachendri Pal</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tenzing Norgay</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Santosh Yadav</t>
+          <t>Slumdog Millionaire</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>Gandhi</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which country launched the world's first satellite?</t>
+          <t>What is India’s first nuclear reactor called?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Dhruva</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>KAMINI</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Apsara</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>CIRUS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Apsara</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
+          <t>Which is the first Indian state to ban plastic completely?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>General V. K. Singh</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>General Manoj Pande</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Admiral Karambir Singh</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>Sikkim</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which was the first programming language?</t>
+          <t>Which was the first Indian movie submitted for the Oscars?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>COBOL</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>Mother India</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in the world?</t>
+          <t>Which is the largest freshwater lake in the world by surface area?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Lake Victoria</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Lake Superior</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which country has the most nuclear weapons as of 2025?</t>
+          <t>Which religion has the most followers in the world?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Christianity</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Islam</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Christianity</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which country has the largest forest area in the world?</t>
+          <t>Which is the largest bird in the world?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Emu</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Ostrich</t>
         </is>
       </c>
     </row>
@@ -4111,662 +4111,662 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which is the world's first novel ever written?</t>
+          <t>Which was the first Indian communication satellite?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Don Quixote</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>APPLESAT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Beowulf</t>
+          <t>INSAT-2A</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Who was the first Indian female IPS officer?</t>
+          <t>What was the world’s first search engine?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Anu Singh</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Radhika Kumari</t>
+          <t>Archie</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pooja Thakur</t>
+          <t>AltaVista</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>Archie</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which city has the most skyscrapers (over 150m)?</t>
+          <t>Which is the first Indian city to have a monorail?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Mumbai</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which is the world’s first democracy?</t>
+          <t>Which Indian river got the status of ‘living entity’ first?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Ganga</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which is India’s first supercomputer?</t>
+          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Shakti</t>
+          <t>General V. K. Singh</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Virgo</t>
+          <t>General Manoj Pande</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mihir</t>
+          <t>Admiral Karambir Singh</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Which was the first Indian express train?</t>
+          <t>Which is the world’s first programmable computer?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Shatabdi Express</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Rajdhani Express</t>
+          <t>Colossus</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>Z3</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Duronto Express</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>Z3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which is the largest island in the world?</t>
+          <t>What was the first smartphone ever made?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>IBM Simon</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>New Guinea</t>
+          <t>Nokia 3310</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Motorola DynaTAC</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>IBM Simon</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which is the deepest lake in the world?</t>
+          <t>Which animal is considered the fastest on land?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Caspian Sea</t>
+          <t>Greyhound</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Cheetah</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which animal is considered the fastest on land?</t>
+          <t>Which is India’s first indigenously built aircraft carrier?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>INS Viraat</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>INS Arihant</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Greyhound</t>
+          <t>INS Trikand</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in India?</t>
+          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Gangtok</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Gangtok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which is the busiest airport in the world by passenger volume?</t>
+          <t>Who was the first woman to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Beijing Capital</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Atlanta (ATL)</t>
+          <t>Rosalind Franklin</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Heathrow</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dubai Intl</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Atlanta (ATL)</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>What is India’s first nuclear reactor called?</t>
+          <t>Which is the longest railway platform in the world?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dhruva</t>
+          <t>Gorakhpur</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>KAMINI</t>
+          <t>Kharagpur</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>Hubballi</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CIRUS</t>
+          <t>Howrah</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>Hubballi</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which is the largest volcano in the world (by volume)?</t>
+          <t>Which city has the most skyscrapers (over 150m)?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mount Fuji</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Eyjafjallajökull</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mount Etna</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>Hong Kong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which mobile phone brand sells the most globally?</t>
+          <t>Who was the first Indian female IPS officer?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Anu Singh</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Radhika Kumari</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Oppo</t>
+          <t>Pooja Thakur</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What was the world’s first search engine?</t>
+          <t>Which was the first Indian company listed on NASDAQ?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AltaVista</t>
+          <t>Satyam</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>Infosys</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>What was the first country to ban plastic bags nationwide?</t>
+          <t>Who was the first Indian to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>C.V. Raman</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which country has the most time zones (including territories)?</t>
+          <t>Which is the smallest state in India by area?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Goa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which was the first country to legalize same-sex marriage?</t>
+          <t>Which is the first Indian city to have a fully underground metro network?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Who was the first President of India?</t>
+          <t>What was the first video game ever created?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Pac-Man</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dr. S. Radhakrishnan</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Tetris</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
     </row>
@@ -4776,182 +4776,182 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of the United Kingdom?</t>
+          <t>Which country has the most nuclear weapons as of 2025?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tony Blair</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which is the smallest mammal by weight?</t>
+          <t>Which country exports the most weapons?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Pygmy Shrew</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mouse Lemur</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pygmy Possum</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which language has the most native speakers in the world?</t>
+          <t>Which Indian city is known as the 'City of Lakes'?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mandarin Chinese</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Mandarin Chinese</t>
+          <t>Udaipur</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which was the first human-made object to reach space?</t>
+          <t>Who was the first female Prime Minister of India?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which is the first Indian state to ban plastic completely?</t>
+          <t>Which is the most downloaded app of all time?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which country has the highest number of Olympic medals overall?</t>
+          <t>Which country is the largest producer of gold?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4961,512 +4961,512 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
           <t>China</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Which is the smallest continent by land area?</t>
+          <t>Which is the smallest country in the world by land area?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>What was the first cloned mammal?</t>
+          <t>Which is the most populated city in the world?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Molly the Cow</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Polly the Pig</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kitty the Cat</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>Tokyo</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Which is the first Indian mission to Mars?</t>
+          <t>Who was the first person to win two Nobel Prizes?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Albert Einstein</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>Linus Pauling</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>IRNSS</t>
+          <t>Erwin Schrödinger</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>What was the first smartphone ever made?</t>
+          <t>Which was the first Indian film?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>Alam Ara</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nokia 3310</t>
+          <t>Sholay</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motorola DynaTAC</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Which is the longest river in the world?</t>
+          <t>Which country has the largest number of active military personnel?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Which is the highest waterfall in the world?</t>
+          <t>Which country has the most volcanoes?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Niagara Falls</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tugela Falls</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Yosemite Falls</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Which was the first Indian movie submitted for the Oscars?</t>
+          <t>Which was the first programming language?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>COBOL</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Fortran</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Assembly</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Fortran</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which Indian city is the first to use electric buses at scale?</t>
+          <t>Which country has the most time zones (including territories)?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which was the first Indian city to be electrified?</t>
+          <t>Which is the tallest animal in the world?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Camel</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>Moose</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>Giraffe</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which is the most used currency in the world?</t>
+          <t>Which is the most visited city in the world (tourism)?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Yen</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pound Sterling</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>Paris</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>What was the first online shopping site?</t>
+          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Dorothy Hodgkin</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Lise Meitner</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which is the first artificial satellite sent into space?</t>
+          <t>Which was the first Indian express train?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>Shatabdi Express</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Vostok</t>
+          <t>Rajdhani Express</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Duronto Express</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank to launch an ATM?</t>
+          <t>Which planet is closest to Earth most often?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ICICI</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Mercury</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which was the first Indian communication satellite?</t>
+          <t>Which is the world's most visited heritage site?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Eiffel Tower</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>APPLESAT</t>
+          <t>Colosseum</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>INSAT-2A</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
     </row>
@@ -5476,627 +5476,627 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Which is the highest mountain peak in the world?</t>
+          <t>Which was the first human-made object to reach space?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Makalu</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Which is the longest national highway in India?</t>
+          <t>Which country has the highest population in the world?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NH7</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>NH27</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>NH19</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Which planet has the most moons?</t>
+          <t>What was the first biosphere reserve in India?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Sundarbans</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Nilgiri</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Nanda Devi</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Manas</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Nilgiri</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Who was the first person to win two Nobel Prizes?</t>
+          <t>Which is the smallest bone in the human body?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Albert Einstein</t>
+          <t>Femur</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Tibia</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Linus Pauling</t>
+          <t>Stapes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Erwin Schrödinger</t>
+          <t>Ulna</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Stapes</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Which was the first movie with sound (talkie)?</t>
+          <t>Who was the first Indian Governor-General of independent India?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>King Kong</t>
+          <t>Lord Mountbatten</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Who was the first Indian Governor-General of independent India?</t>
+          <t>Which is the first country to adopt a national flag?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Lord Mountbatten</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Which is the smallest country in the world by land area?</t>
+          <t>What is the name of India’s first satellite?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Chandrayaan</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Aryabhata</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Which was the first country to reach Mars orbit successfully?</t>
+          <t>Which country has the largest forest area in the world?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>What was the first biosphere reserve in India?</t>
+          <t>Which mobile phone brand sells the most globally?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sundarbans</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nanda Devi</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Manas</t>
+          <t>Oppo</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Which was the first war of Indian independence?</t>
+          <t>Which is the largest species of shark?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>Tiger Shark</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Battle of Plassey</t>
+          <t>Hammerhead Shark</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Battle of Panipat</t>
+          <t>Whale Shark</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Great White Shark</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>Whale Shark</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Which Indian state hosted the first International G20 summit in India?</t>
+          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Amartya Sen</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
+          <t>What was the first online shopping site?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Dorothy Hodgkin</t>
+          <t>NetMarket</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lise Meitner</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>NetMarket</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which is the richest company in the world by market value (2025)?</t>
+          <t>Which city is known as the "Silicon Valley of India"?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Saudi Aramco</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Bangalore</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
+          <t>Which is the most spoken language in India?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Titanic</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>English</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Avengers: Endgame</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Oppenheimer</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>Hindi</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Who was the first person to step on the Moon?</t>
+          <t>Who was the first Indian in space?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Michael Collins</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Which is India’s first indigenously built aircraft carrier?</t>
+          <t>What was the first country to ban plastic bags nationwide?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>INS Viraat</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>INS Arihant</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>INS Trikand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>Rwanda</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Which is the largest ocean in the world by area?</t>
+          <t>Which river carries the most water by volume?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>What was the first ever video uploaded to YouTube?</t>
+          <t>Which was the first movie with sound (talkie)?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>King Kong</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Hello World</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Test Video</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Launch Video</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which religion has the most followers in the world?</t>
+          <t>Who was the first President of India?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Islam</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Dr. S. Radhakrishnan</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
     </row>
@@ -6141,242 +6141,242 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>What was the world's first message sent over the internet?</t>
+          <t>Who was the first President of the world’s first republic (USA)?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>George Washington</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>John Adams</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>George Washington</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Which is the longest railway platform in the world?</t>
+          <t>Which is the longest national highway in India?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Gorakhpur</t>
+          <t>NH44</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Kharagpur</t>
+          <t>NH7</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>NH27</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>NH19</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>NH44</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Which country has the most volcanoes?</t>
+          <t>Which is the coldest place on Earth?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Siberia</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Vostok Station</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Vostok Station</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the "first Smart City"?</t>
+          <t>Which was the world's first artificial satellite?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>Apollo 11</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Luna 2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>Which is the highest waterfall in the world?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Niagara Falls</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Tugela Falls</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Angel Falls</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Yosemite Falls</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Angel Falls</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which river carries the most water by volume?</t>
+          <t>Which was the first nation to reach the South Pole?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Norway</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>What was the first website ever created?</t>
+          <t>Which is the world's first man-made nuclear reactor?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Google.com</t>
+          <t>Fermi-1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Wikipedia.org</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>CERN.ch</t>
+          <t>DIDO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>THTR-300</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
     </row>
@@ -6386,522 +6386,522 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which Indian river got the status of ‘living entity’ first?</t>
+          <t>Which Indian monument has the highest number of tourist visits annually?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Red Fort</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Which is the world’s first university?</t>
+          <t>What was the first computer called?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Nalanda</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>IBM 1401</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al-Qarawiyyin</t>
+          <t>Apple I</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>ENIAC</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Which was the first nation to reach the South Pole?</t>
+          <t>What was the first email ever sent?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Login123</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Which was the first Indian satellite to orbit the Moon?</t>
+          <t>Which is the smallest bird in the world?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Hummingbird</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Parakeet</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>Finch</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Hummingbird</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Which is the most downloaded app of all time?</t>
+          <t>Which was the first war of Indian independence?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Battle of Plassey</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Battle of Panipat</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Which is the tallest building in the world?</t>
+          <t>Who was the first woman Prime Minister in the world?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Shanghai Tower</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>Golda Meir</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Merdeka 118</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>One World Trade Center</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to get an underground metro?</t>
+          <t>Which is the largest desert in the world?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Sahara</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Gobi</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Kalahari</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Which is the hottest planet in the solar system?</t>
+          <t>Which Indian city is known as the "first Smart City"?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Which is the most visited city in the world (tourism)?</t>
+          <t>Which is the most spoken language in the world?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Mandarin</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Which country has the smallest population?</t>
+          <t>Which is the world’s first country to ban tobacco completely?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Bhutan</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Which is the largest continent by land area?</t>
+          <t>What was the first cloned mammal?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Molly the Cow</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Polly the Pig</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Kitty the Cat</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which country has the highest literacy rate?</t>
+          <t>Which is the busiest airport in the world by passenger volume?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Beijing Capital</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Atlanta (ATL)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Heathrow</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Dubai Intl</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Atlanta (ATL)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Which country is the largest producer of gold?</t>
+          <t>Which was the first Indian city to be electrified?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Darjeeling</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Darjeeling</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Which is the smallest bone in the human body?</t>
+          <t>Who was the first Prime Minister of the United Kingdom?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Femur</t>
+          <t>Winston Churchill</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Tibia</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ulna</t>
+          <t>Tony Blair</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Which was the first country to grant women the right to vote?</t>
+          <t>Which is the first Indian mission to Mars?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>IRNSS</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
     </row>
@@ -6911,32 +6911,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which was the world's first artificial satellite?</t>
+          <t>Which country has the largest economy (GDP)?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Apollo 11</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Luna 2</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>USA</t>
         </is>
       </c>
     </row>

--- a/Data/WorldTop.xlsx
+++ b/Data/WorldTop.xlsx
@@ -467,331 +467,331 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Indian state hosted the first International G20 summit in India?</t>
+          <t>Which was the first Indian city to be electrified?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Darjeeling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Darjeeling</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Who invented the first telephone?</t>
+          <t>Which is the longest national highway in India?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>NH44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>NH7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>NH27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guglielmo Marconi</t>
+          <t>NH19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>NH44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which country has the highest number of Olympic medals overall?</t>
+          <t>Which was the first Indian state formed on linguistic basis?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which is the world's first novel ever written?</t>
+          <t>Which is the tallest building in the world?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Don Quixote</t>
+          <t>Shanghai Tower</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>Merdeka 118</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Beowulf</t>
+          <t>One World Trade Center</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which bird is believed to be extinct due to human activity?</t>
+          <t>Which Indian state launched the first electric vehicle policy?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Penguin</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bald Eagle</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>Karnataka</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which was the first Indian state formed on linguistic basis?</t>
+          <t>Which was the first Indian film?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Alam Ara</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Sholay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which is the first country to launch a digital currency?</t>
+          <t>Who was the first female Prime Minister of India?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
+          <t>Which country has the smallest population?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sunil Gavaskar</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sachin Tendulkar</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rahul Dravid</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Who is the first Indian to climb Mount Everest?</t>
+          <t>Who was the first woman Prime Minister in the world?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bachendri Pal</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tenzing Norgay</t>
+          <t>Golda Meir</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Santosh Yadav</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which country has the highest number of billionaires?</t>
+          <t>Which country has the most time zones (including territories)?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -801,262 +801,262 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What was the first website ever created?</t>
+          <t>Which is the smallest bird in the world?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Google.com</t>
+          <t>Hummingbird</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wikipedia.org</t>
+          <t>Parakeet</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CERN.ch</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>Finch</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>Hummingbird</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
+          <t>Which country has the largest forest area in the world?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Titanic</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avengers: Endgame</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oppenheimer</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which is the largest country in the world by area?</t>
+          <t>Which was the first country to reach Mars orbit successfully?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which is the largest mosque in India?</t>
+          <t>What was the first online shopping site?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jama Masjid, Delhi</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mecca Masjid, Hyderabad</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>NetMarket</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nakhoda Masjid, Kolkata</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>NetMarket</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which is the tallest statue in the world?</t>
+          <t>Which city is known as the "Silicon Valley of India"?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Bangalore</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which planet has the most moons?</t>
+          <t>Which is the world's first man-made nuclear reactor?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Fermi-1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>DIDO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>THTR-300</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which is the most used currency in the world?</t>
+          <t>Which is the tallest statue in the world?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yen</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pound Sterling</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
@@ -1066,417 +1066,417 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which was the first car manufacturing company?</t>
+          <t>Which Indian state hosted the first International G20 summit in India?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rolls-Royce</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which was the first country to reach Mars orbit successfully?</t>
+          <t>Which is the hottest planet in the solar system?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Venus</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which is the deepest lake in the world?</t>
+          <t>Which is the first Indian mission to Mars?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Caspian Sea</t>
+          <t>IRNSS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which is the tallest building in the world?</t>
+          <t>What was the first computer called?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shanghai Tower</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Merdeka 118</t>
+          <t>IBM 1401</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>One World Trade Center</t>
+          <t>Apple I</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>ENIAC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
+          <t>Which planet is closest to Earth most often?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IIT Delhi</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IIT Bombay</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IIT Madras</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>Mercury</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank?</t>
+          <t>Who was the first Indian Governor-General of independent India?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>Lord Mountbatten</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Allahabad Bank</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which is the world’s oldest living city?</t>
+          <t>Which animal is considered the fastest on land?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Greyhound</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Cheetah</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which is the largest ocean in the world by area?</t>
+          <t>Which is the world’s oldest living city?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Varanasi</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which is the largest dam in India by volume?</t>
+          <t>Which was the first car manufacturing company?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sardar Sarovar Dam</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bhakra Nangal</t>
+          <t>Peugeot</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Rolls-Royce</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Peugeot</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which language has the most native speakers in the world?</t>
+          <t>Which Indian city is known as the "first Smart City"?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mandarin Chinese</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mandarin Chinese</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Who was the first person to receive Bharat Ratna?</t>
+          <t>Which was the first country to grant women the right to vote?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S. Radhakrishnan</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which is the world’s first university?</t>
+          <t>Which is India’s first supercomputer?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nalanda</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>Shakti</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Virgo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al-Qarawiyyin</t>
+          <t>Mihir</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
     </row>
@@ -1486,942 +1486,942 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Who was the first Indian Miss World?</t>
+          <t>Which is the coldest place on Earth?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sushmita Sen</t>
+          <t>Siberia</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lara Dutta</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>Vostok Station</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aishwarya Rai</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>Vostok Station</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What was the first successful vaccine developed for?</t>
+          <t>Which country has the most volcanoes?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which is the highest mountain peak in the world?</t>
+          <t>Which is the most visited city in the world (tourism)?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Makalu</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>Paris</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman in space?</t>
+          <t>What was the first smartphone ever made?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>IBM Simon</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Nokia 3310</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ritu Karidhal</t>
+          <t>Motorola DynaTAC</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>IBM Simon</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
+          <t>Which was the first Indian movie submitted for the Oscars?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Saina Nehwal</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P. V. Sindhu</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mary Kom</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>Mother India</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which is the deepest ocean in the world?</t>
+          <t>Who is the first Indian to climb Mount Everest?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>Bachendri Pal</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>Tenzing Norgay</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>Santosh Yadav</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which is India’s first supercomputer?</t>
+          <t>Which country has the most lakes?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Shakti</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virgo</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mihir</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What was the first country to recognize the United States as independent?</t>
+          <t>Which Indian city is the first to use electric buses at scale?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Pune</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which is the smallest mammal by weight?</t>
+          <t>Which is the first country to implement a constitution?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pygmy Shrew</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mouse Lemur</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pygmy Possum</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank to launch an ATM?</t>
+          <t>Which planet has the most moons?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ICICI</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Saturn</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to implement the GST?</t>
+          <t>Which is the world’s first programmable computer?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Colossus</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Z3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Z3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What was the first ever video uploaded to YouTube?</t>
+          <t>Which is the largest volcano in the world (by volume)?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>Mount Fuji</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Hello World</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Test Video</t>
+          <t>Eyjafjallajökull</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Launch Video</t>
+          <t>Mount Etna</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to get an underground metro?</t>
+          <t>Which is the largest state in India by area?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Rajasthan</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which is the largest state in India by area?</t>
+          <t>Which country has the highest GDP in the world?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which was the first country to legalize same-sex marriage?</t>
+          <t>What is India’s first nuclear reactor called?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Dhruva</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>KAMINI</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Apsara</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>CIRUS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Apsara</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which country has the most lakes?</t>
+          <t>Which is the smallest continent by land area?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which was the first Indian satellite to orbit the Moon?</t>
+          <t>Which is the deepest ocean in the world?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Indian state launched the first electric vehicle policy?</t>
+          <t>What was the first country to ban plastic bags nationwide?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Rwanda</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which was the first country to use paper money?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who was the first person to step on the Moon?</t>
+          <t>Which country launched the world's first satellite?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Michael Collins</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which is the smallest continent by land area?</t>
+          <t>Which is the longest railway platform in the world?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Gorakhpur</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Kharagpur</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Hubballi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Howrah</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Hubballi</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which was the first messaging app?</t>
+          <t>Which is India’s first indigenously built aircraft carrier?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>INS Viraat</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AIM</t>
+          <t>INS Arihant</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>INS Trikand</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>Who invented the first airplane?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Leonardo da Vinci</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Charles Lindbergh</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which is the first country to implement a constitution?</t>
+          <t>Who was the first person to step on the Moon?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Michael Collins</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which is the most downloaded game of all time?</t>
+          <t>Which country has the highest number of billionaires?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PUBG</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Candy Crush</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Minecraft</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to achieve 100% literacy?</t>
+          <t>Who invented the first electric light bulb?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Michael Faraday</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which is the largest island in the world?</t>
+          <t>Which was the world's first artificial satellite?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Apollo 11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>New Guinea</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Luna 2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>
@@ -2431,417 +2431,417 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which was the first animated feature film?</t>
+          <t>Which is the largest dam in India by volume?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cinderella</t>
+          <t>Sardar Sarovar Dam</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pinocchio</t>
+          <t>Bhakra Nangal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bambi</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of India?</t>
+          <t>What was the first website ever created?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Google.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sardar Patel</t>
+          <t>Wikipedia.org</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>CERN.ch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which is the first country to make education compulsory by law?</t>
+          <t>Which was the first Indian film to win an Oscar?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Slumdog Millionaire</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Gandhi</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which Indian river has the largest length within India?</t>
+          <t>Who was the first person to go to space?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brahmaputra</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which is the world's first language (known oldest)?</t>
+          <t>Which is the most downloaded game of all time?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>PUBG</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Candy Crush</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Minecraft</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What was the world's first message sent over the internet?</t>
+          <t>Which was the first nation to reach the South Pole?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>Norway</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which country has the highest GDP in the world?</t>
+          <t>Which is the world’s first university?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Nalanda</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Takshashila</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Al-Qarawiyyin</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Takshashila</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Who was the first woman ruler of India?</t>
+          <t>Which is the largest continent by land area?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rani Lakshmibai</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ahilyabai Holkar</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Who was India’s first female President?</t>
+          <t>Which mobile phone brand sells the most globally?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>Oppo</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which is the oldest dam in India still in use?</t>
+          <t>Which river carries the most water by volume?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mettur Dam</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Krishna Raja Sagara Dam</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which country has the smallest population?</t>
+          <t>Which is the most spoken language in the world?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Mandarin</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which is the hottest planet in the solar system?</t>
+          <t>Which is the most spoken language in India?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>English</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Hindi</t>
         </is>
       </c>
     </row>
@@ -2851,32 +2851,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which Indian airport is the busiest by passenger traffic?</t>
+          <t>Which was the first city to host the modern Olympic Games?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kempegowda Intl (Bangalore)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi Intl (Hyderabad)</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
@@ -2886,802 +2886,802 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Who was the first human in space?</t>
+          <t>Which is the world's most visited heritage site?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Eiffel Tower</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Colosseum</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>Which Indian state has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which Indian city is the first to use electric buses at scale?</t>
+          <t>Which country has the highest population in the world?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Indian was the first to win an Olympic gold medal?</t>
+          <t>Which is the first artificial satellite sent into space?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>Vostok</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Major Dhyan Chand</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KD Jadhav</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which was the first country to grant women the right to vote?</t>
+          <t>Who was the first Indian Miss World?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sushmita Sen</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Lara Dutta</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Reita Faria</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Aishwarya Rai</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Reita Faria</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Indian state has the highest literacy rate?</t>
+          <t>Which is the largest freshwater lake in the world by surface area?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Lake Victoria</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Lake Superior</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which is the largest continent by land area?</t>
+          <t>Which Indian monument has the highest number of tourist visits annually?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Red Fort</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which is the richest company in the world by market value (2025)?</t>
+          <t>Which was the first human-made object to reach space?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Saudi Aramco</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which is the world’s first democracy?</t>
+          <t>What was the first object sold on eBay?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Wristwatch</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Comic Book</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Who was the first person to go to space?</t>
+          <t>Who was the first President of the world’s first republic (USA)?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>George Washington</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>John Adams</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>George Washington</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
+          <t>Which was the first country to use paper money?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Neeraj Chopra</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hima Das</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Anju George</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which country launched the world's first satellite?</t>
+          <t>Which is the smallest state in India by area?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Goa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What was the first object sold on eBay?</t>
+          <t>Which was the first Indian satellite to orbit the Moon?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wristwatch</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Comic Book</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which country produces the most oil?</t>
+          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>General V. K. Singh</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>General Manoj Pande</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Admiral Karambir Singh</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Who invented the first airplane?</t>
+          <t>Which is the world’s first country to ban tobacco completely?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Charles Lindbergh</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>Bhutan</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>What is the world’s tallest statue as of 2025?</t>
+          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Gangtok</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Gangtok</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which is the longest river in the world?</t>
+          <t>What was the first ever video uploaded to YouTube?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>Hello World</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Test Video</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Launch Video</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which is the first artificial satellite sent into space?</t>
+          <t>What was the world’s first printed book?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>The Holy Bible</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Vostok</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Quran</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What was the name of the first computer virus?</t>
+          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ILOVEYOU</t>
+          <t>IIT Delhi</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>IIT Bombay</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Stuxnet</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>WannaCry</t>
+          <t>IIT Madras</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What was the world’s first printed book?</t>
+          <t>What was the world’s first search engine?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>The Holy Bible</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Archie</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Quran</t>
+          <t>AltaVista</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Archie</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which country has the highest literacy rate?</t>
+          <t>Who was the first Prime Minister of India?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sardar Patel</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who was the first woman to fly solo around the world?</t>
+          <t>Which is the most downloaded app of all time?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Valentina Tereshkova</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Anne Morrow</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Who invented the first electric light bulb?</t>
+          <t>Which is the largest desert in the world?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>Sahara</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Michael Faraday</t>
+          <t>Gobi</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Kalahari</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
     </row>
@@ -3691,767 +3691,767 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which country has the longest coastline?</t>
+          <t>Which is the first Indian city to have a monorail?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mumbai</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which was the first city to host the modern Olympic Games?</t>
+          <t>Who was India’s first female President?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which is the largest volcano in the world (by volume)?</t>
+          <t>Which is the first country to adopt a national flag?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mount Fuji</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Eyjafjallajökull</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mount Etna</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which is the fastest bird in the world?</t>
+          <t>Who was the first Prime Minister of the United Kingdom?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Golden Eagle</t>
+          <t>Winston Churchill</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Swan</t>
+          <t>Tony Blair</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which is the largest mammal in the world?</t>
+          <t>Which was the first Indian company listed on NASDAQ?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>African Elephant</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hippopotamus</t>
+          <t>Satyam</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>Infosys</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which was the first Indian film to win an Oscar?</t>
+          <t>What is the world’s tallest statue as of 2025?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Slumdog Millionaire</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What is India’s first nuclear reactor called?</t>
+          <t>Which is the largest bird in the world?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dhruva</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KAMINI</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CIRUS</t>
+          <t>Emu</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>Ostrich</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which is the first Indian state to ban plastic completely?</t>
+          <t>Which is the smallest bone in the human body?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Femur</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Tibia</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Stapes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Ulna</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Stapes</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which was the first Indian movie submitted for the Oscars?</t>
+          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>Titanic</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>Avatar</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Avengers: Endgame</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Oppenheimer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Avatar</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which is the largest freshwater lake in the world by surface area?</t>
+          <t>Which is the smallest country in the world by land area?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lake Victoria</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which religion has the most followers in the world?</t>
+          <t>Which was the first messaging app?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Islam</t>
+          <t>ICQ</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>AIM</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>ICQ</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which is the largest bird in the world?</t>
+          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Albatross</t>
+          <t>Amartya Sen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Emu</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which was the first Indian communication satellite?</t>
+          <t>Which is the most used currency in the world?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Yen</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>APPLESAT</t>
+          <t>US Dollar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>INSAT-2A</t>
+          <t>Pound Sterling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>US Dollar</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>What was the world’s first search engine?</t>
+          <t>Which country exports the most weapons?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AltaVista</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a monorail?</t>
+          <t>What was the first cloned mammal?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Molly the Cow</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Polly the Pig</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Kitty the Cat</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which Indian river got the status of ‘living entity’ first?</t>
+          <t>Which religion has the most followers in the world?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Christianity</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Islam</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Christianity</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
+          <t>Which city has the most skyscrapers (over 150m)?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>General V. K. Singh</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>General Manoj Pande</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Admiral Karambir Singh</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>Hong Kong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Which is the world’s first programmable computer?</t>
+          <t>Which country has the highest number of Olympic medals overall?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Colossus</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>What was the first smartphone ever made?</t>
+          <t>Which was the first country to legalize same-sex marriage?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Nokia 3310</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motorola DynaTAC</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>Netherlands</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which animal is considered the fastest on land?</t>
+          <t>Who was the first woman to fly solo around the world?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Valentina Tereshkova</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Greyhound</t>
+          <t>Anne Morrow</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which is India’s first indigenously built aircraft carrier?</t>
+          <t>Which is the largest island in the world?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>INS Viraat</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>INS Arihant</t>
+          <t>New Guinea</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>INS Trikand</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>Greenland</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
+          <t>Which is the first country to make education compulsory by law?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
@@ -4461,662 +4461,662 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Who was the first woman to win a Nobel Prize?</t>
+          <t>Which is the largest country in the world by area?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Rosalind Franklin</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which is the longest railway platform in the world?</t>
+          <t>Which is the first country to launch a digital currency?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Gorakhpur</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Kharagpur</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Bahamas</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which city has the most skyscrapers (over 150m)?</t>
+          <t>Which is the tallest animal in the world?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Camel</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Moose</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Giraffe</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Who was the first Indian female IPS officer?</t>
+          <t>What was the first country to recognize the United States as independent?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Anu Singh</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Radhika Kumari</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Pooja Thakur</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>Morocco</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which was the first Indian company listed on NASDAQ?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Satyam</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a Nobel Prize?</t>
+          <t>What was the first successful vaccine developed for?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>C.V. Raman</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Smallpox</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Smallpox</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which is the smallest state in India by area?</t>
+          <t>Which is the first Indian city to have a fully underground metro network?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a fully underground metro network?</t>
+          <t>Which is the fastest bird in the world?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Golden Eagle</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Swan</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>What was the first video game ever created?</t>
+          <t>Which Indian state was the first to implement the GST?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Pac-Man</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tetris</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Assam</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which country has the most nuclear weapons as of 2025?</t>
+          <t>Which Indian river got the status of ‘living entity’ first?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Ganga</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which country exports the most weapons?</t>
+          <t>Which is the highest waterfall in the world?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Niagara Falls</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Tugela Falls</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Angel Falls</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Yosemite Falls</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Angel Falls</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the 'City of Lakes'?</t>
+          <t>Which is the first Indian bank to launch an ATM?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>ICICI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>HSBC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Who was the first female Prime Minister of India?</t>
+          <t>Which was the first movie with sound (talkie)?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>King Kong</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which is the most downloaded app of all time?</t>
+          <t>Which was the first Indian communication satellite?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>APPLESAT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>INSAT-2A</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which country is the largest producer of gold?</t>
+          <t>Which country produces the most oil?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Which is the smallest country in the world by land area?</t>
+          <t>Who invented the first telephone?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Alexander Graham Bell</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Guglielmo Marconi</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>Alexander Graham Bell</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Which is the most populated city in the world?</t>
+          <t>Who was the first President of India?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Dr. S. Radhakrishnan</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Who was the first person to win two Nobel Prizes?</t>
+          <t>Which is the richest company in the world by market value (2025)?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Albert Einstein</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Linus Pauling</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Erwin Schrödinger</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Which was the first Indian film?</t>
+          <t>What was the world's first message sent over the internet?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Alam Ara</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sholay</t>
+          <t>LO</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>LO</t>
         </is>
       </c>
     </row>
@@ -5126,102 +5126,102 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Which country has the largest number of active military personnel?</t>
+          <t>What was the name of the first computer virus?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>ILOVEYOU</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Creeper</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Stuxnet</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>WannaCry</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Creeper</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Which country has the most volcanoes?</t>
+          <t>Which is the most populated city in the world?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Tokyo</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Which was the first programming language?</t>
+          <t>Which is the world’s first democracy?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>COBOL</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
@@ -5231,172 +5231,172 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which country has the most time zones (including territories)?</t>
+          <t>Which country has the longest coastline?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which is the tallest animal in the world?</t>
+          <t>Which is the oldest dam in India still in use?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Mettur Dam</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Krishna Raja Sagara Dam</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Camel</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Moose</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which is the most visited city in the world (tourism)?</t>
+          <t>Which country has the most nuclear weapons as of 2025?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
+          <t>Which is the largest ocean in the world by area?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Dorothy Hodgkin</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lise Meitner</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which was the first Indian express train?</t>
+          <t>Which is the deepest lake in the world?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Shatabdi Express</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Rajdhani Express</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Duronto Express</t>
+          <t>Caspian Sea</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
     </row>
@@ -5406,277 +5406,277 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which planet is closest to Earth most often?</t>
+          <t>Who was the first person to win two Nobel Prizes?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Albert Einstein</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Linus Pauling</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Erwin Schrödinger</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which is the world's most visited heritage site?</t>
+          <t>Which was the first Indian express train?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Shatabdi Express</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Eiffel Tower</t>
+          <t>Rajdhani Express</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Colosseum</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>Duronto Express</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Which was the first human-made object to reach space?</t>
+          <t>Which Indian state was the first to achieve 100% literacy?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Which country has the highest population in the world?</t>
+          <t>Who was the first woman ruler of India?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Rani Lakshmibai</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Ahilyabai Holkar</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>What was the first biosphere reserve in India?</t>
+          <t>Which was the first animated feature film?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Sundarbans</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>Cinderella</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Nanda Devi</t>
+          <t>Pinocchio</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Manas</t>
+          <t>Bambi</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Which is the smallest bone in the human body?</t>
+          <t>Who was the first woman to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Femur</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tibia</t>
+          <t>Rosalind Franklin</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ulna</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Who was the first Indian Governor-General of independent India?</t>
+          <t>Who was the first Indian to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Lord Mountbatten</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>C.V. Raman</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which is the first country to adopt a national flag?</t>
+          <t>Which is the world's first language (known oldest)?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sumerian</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Sumerian</t>
         </is>
       </c>
     </row>
@@ -5717,1051 +5717,1051 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Which country has the largest forest area in the world?</t>
+          <t>Which Indian was the first to win an Olympic gold medal?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Major Dhyan Chand</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>KD Jadhav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Which mobile phone brand sells the most globally?</t>
+          <t>Which is the highest mountain peak in the world?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Oppo</t>
+          <t>Makalu</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Mount Everest</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Which is the largest species of shark?</t>
+          <t>Which is the longest river in the world?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tiger Shark</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Hammerhead Shark</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Great White Shark</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>Nile</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
+          <t>Who was the first human in space?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Amartya Sen</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>What was the first online shopping site?</t>
+          <t>Which is the first Indian bank?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Allahabad Bank</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which city is known as the "Silicon Valley of India"?</t>
+          <t>Which is the world's first novel ever written?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Don Quixote</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Beowulf</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in India?</t>
+          <t>Which is the largest mammal in the world?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>African Elephant</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>Blue Whale</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hippopotamus</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Blue Whale</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Who was the first Indian in space?</t>
+          <t>Which Indian airport is the busiest by passenger traffic?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>Kempegowda Intl (Bangalore)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>Rajiv Gandhi Intl (Hyderabad)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>What was the first country to ban plastic bags nationwide?</t>
+          <t>Which country has the largest economy (GDP)?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Which river carries the most water by volume?</t>
+          <t>Who was the first person to receive Bharat Ratna?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>S. Radhakrishnan</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which was the first movie with sound (talkie)?</t>
+          <t>Which Indian river has the largest length within India?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>King Kong</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Brahmaputra</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>Ganga</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Who was the first President of India?</t>
+          <t>Which country is the largest producer of gold?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Dr. S. Radhakrishnan</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Who was the first President of the world’s first republic (USA)?</t>
+          <t>Which Indian city is known as the 'City of Lakes'?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>John Adams</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>Udaipur</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Which is the longest national highway in India?</t>
+          <t>Who was the first Indian in space?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NH7</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>NH27</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NH19</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Which is the coldest place on Earth?</t>
+          <t>Which was the first programming language?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Siberia</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>COBOL</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Fortran</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Assembly</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Fortran</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Which was the world's first artificial satellite?</t>
+          <t>Which is the smallest mammal by weight?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Apollo 11</t>
+          <t>Pygmy Shrew</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Mouse Lemur</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Luna 2</t>
+          <t>Pygmy Possum</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Which is the highest waterfall in the world?</t>
+          <t>Which country has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Niagara Falls</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tugela Falls</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Yosemite Falls</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>Andorra</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which was the first nation to reach the South Pole?</t>
+          <t>What was the first biosphere reserve in India?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sundarbans</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Nilgiri</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Nanda Devi</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Manas</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Nilgiri</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which is the world's first man-made nuclear reactor?</t>
+          <t>Who was the first Indian woman in space?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Fermi-1</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>DIDO</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>THTR-300</t>
+          <t>Ritu Karidhal</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which Indian monument has the highest number of tourist visits annually?</t>
+          <t>Which bird is believed to be extinct due to human activity?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Penguin</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Red Fort</t>
+          <t>Bald Eagle</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Dodo</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Dodo</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>What was the first computer called?</t>
+          <t>Which is the largest species of shark?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>Tiger Shark</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>Hammerhead Shark</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>IBM 1401</t>
+          <t>Whale Shark</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Apple I</t>
+          <t>Great White Shark</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>Whale Shark</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>What was the first email ever sent?</t>
+          <t>Who was the first Indian female IPS officer?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Anu Singh</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>Radhika Kumari</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Login123</t>
+          <t>Pooja Thakur</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Which is the smallest bird in the world?</t>
+          <t>Which is the first Indian city to get an underground metro?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Parakeet</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Finch</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Which was the first war of Indian independence?</t>
+          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>Sunil Gavaskar</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Battle of Plassey</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Battle of Panipat</t>
+          <t>Sachin Tendulkar</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Rahul Dravid</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Who was the first woman Prime Minister in the world?</t>
+          <t>Which language has the most native speakers in the world?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Golda Meir</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>Mandarin Chinese</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>Mandarin Chinese</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Which is the largest desert in the world?</t>
+          <t>Which is the largest mosque in India?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sahara</t>
+          <t>Jama Masjid, Delhi</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Gobi</t>
+          <t>Mecca Masjid, Hyderabad</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Kalahari</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>Nakhoda Masjid, Kolkata</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the "first Smart City"?</t>
+          <t>What was the first video game ever created?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>Pac-Man</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Tetris</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in the world?</t>
+          <t>What was the first email ever sent?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Login123</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Which is the world’s first country to ban tobacco completely?</t>
+          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Dorothy Hodgkin</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Lise Meitner</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>What was the first cloned mammal?</t>
+          <t>Which was the first war of Indian independence?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Molly the Cow</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Polly the Pig</t>
+          <t>Battle of Plassey</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>Battle of Panipat</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kitty the Cat</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
     </row>
@@ -6802,141 +6802,141 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Which was the first Indian city to be electrified?</t>
+          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Neeraj Chopra</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Hima Das</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>Anju George</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of the United Kingdom?</t>
+          <t>Which country has the largest number of active military personnel?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tony Blair</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Which is the first Indian mission to Mars?</t>
+          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Saina Nehwal</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>P. V. Sindhu</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>IRNSS</t>
+          <t>Mary Kom</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which country has the largest economy (GDP)?</t>
+          <t>Which is the first Indian state to ban plastic completely?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sikkim</t>
         </is>
       </c>
     </row>

--- a/Data/WorldTop.xlsx
+++ b/Data/WorldTop.xlsx
@@ -467,176 +467,176 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which was the first Indian city to be electrified?</t>
+          <t>Which is the largest mosque in India?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Jama Masjid, Delhi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Mecca Masjid, Hyderabad</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>Nakhoda Masjid, Kolkata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Darjeeling</t>
+          <t>Taj-ul-Masajid, Bhopal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which is the longest national highway in India?</t>
+          <t>What was the first video game ever created?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>Pong</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NH7</t>
+          <t>Pac-Man</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NH27</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NH19</t>
+          <t>Tetris</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NH44</t>
+          <t>Tennis for Two</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which was the first Indian state formed on linguistic basis?</t>
+          <t>What was the first email ever sent?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Login123</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>QWERTYUIOP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which is the tallest building in the world?</t>
+          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shanghai Tower</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Merdeka 118</t>
+          <t>Dorothy Hodgkin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>One World Trade Center</t>
+          <t>Lise Meitner</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Burj Khalifa</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which Indian state launched the first electric vehicle policy?</t>
+          <t>Which was the first war of Indian independence?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Battle of Plassey</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Battle of Panipat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Champaran Movement</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>1857 Revolt</t>
         </is>
       </c>
     </row>
@@ -646,1537 +646,1537 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which was the first Indian film?</t>
+          <t>Which is the busiest airport in the world by passenger volume?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alam Ara</t>
+          <t>Beijing Capital</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Atlanta (ATL)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sholay</t>
+          <t>Heathrow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>Dubai Intl</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Atlanta (ATL)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who was the first female Prime Minister of India?</t>
+          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>Neeraj Chopra</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Hima Das</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Anju George</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which country has the smallest population?</t>
+          <t>Which country has the largest number of active military personnel?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Who was the first woman Prime Minister in the world?</t>
+          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Golda Meir</t>
+          <t>Saina Nehwal</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>P. V. Sindhu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>Mary Kom</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sirimavo Bandaranaike</t>
+          <t>Karnam Malleswari</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which country has the most time zones (including territories)?</t>
+          <t>Which is the first Indian state to ban plastic completely?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Sikkim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which is the smallest bird in the world?</t>
+          <t>Which is the smallest mammal by weight?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Parakeet</t>
+          <t>Pygmy Shrew</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Mouse Lemur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finch</t>
+          <t>Pygmy Possum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Bumblebee Bat</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which country has the largest forest area in the world?</t>
+          <t>Which country has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Andorra</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which was the first country to reach Mars orbit successfully?</t>
+          <t>What was the first biosphere reserve in India?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Sundarbans</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Nilgiri</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Nanda Devi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Manas</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Nilgiri</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What was the first online shopping site?</t>
+          <t>Who was the first Indian woman in space?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Ritu Karidhal</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NetMarket</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which city is known as the "Silicon Valley of India"?</t>
+          <t>Which bird is believed to be extinct due to human activity?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Penguin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bald Eagle</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dodo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Dodo</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which is the world's first man-made nuclear reactor?</t>
+          <t>Which is the largest species of shark?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fermi-1</t>
+          <t>Tiger Shark</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>Hammerhead Shark</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DIDO</t>
+          <t>Whale Shark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>THTR-300</t>
+          <t>Great White Shark</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chicago Pile-1</t>
+          <t>Whale Shark</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which is the tallest statue in the world?</t>
+          <t>Who was the first Indian female IPS officer?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>Anu Singh</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Radhika Kumari</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Pooja Thakur</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Kiran Bedi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Indian state hosted the first International G20 summit in India?</t>
+          <t>Which is the first Indian city to get an underground metro?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which is the hottest planet in the solar system?</t>
+          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Sunil Gavaskar</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Sachin Tendulkar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Rahul Dravid</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Virender Sehwag</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which is the first Indian mission to Mars?</t>
+          <t>Which language has the most native speakers in the world?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>Mandarin Chinese</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IRNSS</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>Mandarin Chinese</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What was the first computer called?</t>
+          <t>Which is the world's first novel ever written?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>Don Quixote</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IBM 1401</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Apple I</t>
+          <t>Beowulf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>The Tale of Genji</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which planet is closest to Earth most often?</t>
+          <t>Which is the largest mammal in the world?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>African Elephant</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Blue Whale</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Hippopotamus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Blue Whale</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who was the first Indian Governor-General of independent India?</t>
+          <t>Which Indian airport is the busiest by passenger traffic?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lord Mountbatten</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Kempegowda Intl (Bangalore)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Rajiv Gandhi Intl (Hyderabad)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Indira Gandhi Intl (Delhi)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which animal is considered the fastest on land?</t>
+          <t>Which country has the largest economy (GDP)?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Greyhound</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which is the world’s oldest living city?</t>
+          <t>Who was the first person to receive Bharat Ratna?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>S. Radhakrishnan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which was the first car manufacturing company?</t>
+          <t>Which Indian river has the largest length within India?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rolls-Royce</t>
+          <t>Brahmaputra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>Ganga</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the "first Smart City"?</t>
+          <t>Which country is the largest producer of gold?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gandhinagar</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>China</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which was the first country to grant women the right to vote?</t>
+          <t>Which Indian city is known as the 'City of Lakes'?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Udaipur</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which is India’s first supercomputer?</t>
+          <t>Who was the first Indian in space?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Shakti</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virgo</t>
+          <t>Sunita Williams</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mihir</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PARAM 8000</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which is the coldest place on Earth?</t>
+          <t>Which was the first programming language?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Siberia</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>COBOL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Fortran</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Assembly</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Vostok Station</t>
+          <t>Fortran</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which country has the most volcanoes?</t>
+          <t>Which was the first animated feature film?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Cinderella</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Pinocchio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Bambi</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Snow White and the Seven Dwarfs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which is the most visited city in the world (tourism)?</t>
+          <t>Who was the first woman to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Rosalind Franklin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Ada Lovelace</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What was the first smartphone ever made?</t>
+          <t>Who was the first Indian to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>iPhone</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>C.V. Raman</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nokia 3310</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motorola DynaTAC</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IBM Simon</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which was the first Indian movie submitted for the Oscars?</t>
+          <t>Which is the world's first language (known oldest)?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pather Panchali</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Harishchandra</t>
+          <t>Sumerian</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>Sumerian</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who is the first Indian to climb Mount Everest?</t>
+          <t>What is the name of India’s first satellite?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bachendri Pal</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tenzing Norgay</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santosh Yadav</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>Chandrayaan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Avtar Singh Cheema</t>
+          <t>Aryabhata</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which country has the most lakes?</t>
+          <t>Which Indian was the first to win an Olympic gold medal?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Milkha Singh</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Major Dhyan Chand</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>KD Jadhav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Abhinav Bindra</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which Indian city is the first to use electric buses at scale?</t>
+          <t>Which is the highest mountain peak in the world?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Makalu</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Mount Everest</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which is the first country to implement a constitution?</t>
+          <t>Which is the longest river in the world?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Nile</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which planet has the most moons?</t>
+          <t>Who was the first human in space?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which is the world’s first programmable computer?</t>
+          <t>Which is the first Indian bank?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENIAC</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Colossus</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UNIVAC</t>
+          <t>Allahabad Bank</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>Bank of Bombay</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which is the largest volcano in the world (by volume)?</t>
+          <t>Which is the world’s first democracy?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mount Fuji</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Eyjafjallajökull</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mount Etna</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Mauna Loa</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which is the largest state in India by area?</t>
+          <t>Which country has the longest coastline?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which country has the highest GDP in the world?</t>
+          <t>Which is the oldest dam in India still in use?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mettur Dam</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Krishna Raja Sagara Dam</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Kallanai Dam</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What is India’s first nuclear reactor called?</t>
+          <t>Which country has the most nuclear weapons as of 2025?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dhruva</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KAMINI</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CIRUS</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Apsara</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which is the smallest continent by land area?</t>
+          <t>Which is the largest ocean in the world by area?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which is the deepest ocean in the world?</t>
+          <t>Which is the deepest lake in the world?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Caspian Sea</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What was the first country to ban plastic bags nationwide?</t>
+          <t>Who was the first person to win two Nobel Prizes?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Albert Einstein</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Marie Curie</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Linus Pauling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Erwin Schrödinger</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Marie Curie</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>Which was the first Indian express train?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Shatabdi Express</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Rajdhani Express</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Duronto Express</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Deccan Queen</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which country launched the world's first satellite?</t>
+          <t>Which Indian state was the first to achieve 100% literacy?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
@@ -2186,152 +2186,152 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which is the longest railway platform in the world?</t>
+          <t>Who was the first woman ruler of India?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gorakhpur</t>
+          <t>Rani Lakshmibai</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Kharagpur</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Ahilyabai Holkar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hubballi</t>
+          <t>Razia Sultana</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which is India’s first indigenously built aircraft carrier?</t>
+          <t>Which is the first Indian bank to launch an ATM?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INS Viraat</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>INS Arihant</t>
+          <t>ICICI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>INS Trikand</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>INS Vikrant</t>
+          <t>HSBC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Who invented the first airplane?</t>
+          <t>Which was the first movie with sound (talkie)?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>King Kong</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Charles Lindbergh</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Wright Brothers</t>
+          <t>The Jazz Singer</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Who was the first person to step on the Moon?</t>
+          <t>Which was the first Indian communication satellite?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>APPLESAT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Michael Collins</t>
+          <t>INSAT-2A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which country has the highest number of billionaires?</t>
+          <t>Which country produces the most oil?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2357,891 +2357,891 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Who invented the first electric light bulb?</t>
+          <t>Who invented the first telephone?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>Thomas Edison</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Alexander Graham Bell</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Nikola Tesla</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Michael Faraday</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Thomas Edison</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Guglielmo Marconi</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Alexander Graham Bell</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which was the world's first artificial satellite?</t>
+          <t>Who was the first President of India?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apollo 11</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Dr. S. Radhakrishnan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luna 2</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which is the largest dam in India by volume?</t>
+          <t>Which is the richest company in the world by market value (2025)?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sardar Sarovar Dam</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bhakra Nangal</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What was the first website ever created?</t>
+          <t>What was the world's first message sent over the internet?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Google.com</t>
+          <t>Hello</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wikipedia.org</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CERN.ch</t>
+          <t>LO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>info.cern.ch</t>
+          <t>LO</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which was the first Indian film to win an Oscar?</t>
+          <t>What was the name of the first computer virus?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mother India</t>
+          <t>ILOVEYOU</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lagaan</t>
+          <t>Creeper</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Slumdog Millionaire</t>
+          <t>Stuxnet</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>WannaCry</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Creeper</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Who was the first person to go to space?</t>
+          <t>Which is the most populated city in the world?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Tokyo</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which is the most downloaded game of all time?</t>
+          <t>Which is the first country to launch a digital currency?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PUBG</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Candy Crush</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Minecraft</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Subway Surfers</t>
+          <t>Bahamas</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which was the first nation to reach the South Pole?</t>
+          <t>Which is the tallest animal in the world?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Camel</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Moose</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Giraffe</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which is the world’s first university?</t>
+          <t>What was the first country to recognize the United States as independent?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nalanda</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al-Qarawiyyin</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Takshashila</t>
+          <t>Morocco</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which is the largest continent by land area?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which mobile phone brand sells the most globally?</t>
+          <t>What was the first successful vaccine developed for?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oppo</t>
+          <t>Smallpox</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Smallpox</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which river carries the most water by volume?</t>
+          <t>Which is the first Indian city to have a fully underground metro network?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Kolkata</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in the world?</t>
+          <t>Which is the fastest bird in the world?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Golden Eagle</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Swan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Peregrine Falcon</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which is the most spoken language in India?</t>
+          <t>Which Indian state was the first to implement the GST?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Assam</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which was the first city to host the modern Olympic Games?</t>
+          <t>Which Indian river got the status of ‘living entity’ first?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>Ganga</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which is the world's most visited heritage site?</t>
+          <t>Which is the highest waterfall in the world?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Niagara Falls</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Eiffel Tower</t>
+          <t>Tugela Falls</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Colosseum</t>
+          <t>Angel Falls</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>Yosemite Falls</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Great Wall of China</t>
+          <t>Angel Falls</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which Indian state has the highest literacy rate?</t>
+          <t>Which country exports the most weapons?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which country has the highest population in the world?</t>
+          <t>What was the first cloned mammal?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Molly the Cow</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Polly the Pig</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Kitty the Cat</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Dolly the Sheep</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which is the first artificial satellite sent into space?</t>
+          <t>Which religion has the most followers in the world?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>Christianity</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Vostok</t>
+          <t>Islam</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Christianity</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Who was the first Indian Miss World?</t>
+          <t>Which city has the most skyscrapers (over 150m)?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sushmita Sen</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lara Dutta</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aishwarya Rai</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Reita Faria</t>
+          <t>Hong Kong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which is the largest freshwater lake in the world by surface area?</t>
+          <t>Which country has the highest number of Olympic medals overall?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lake Victoria</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which Indian monument has the highest number of tourist visits annually?</t>
+          <t>Which was the first country to legalize same-sex marriage?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Red Fort</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Netherlands</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which was the first human-made object to reach space?</t>
+          <t>Who was the first woman to fly solo around the world?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sputnik 1</t>
+          <t>Valentina Tereshkova</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Apollo 1</t>
+          <t>Kalpana Chawla</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Explorer 1</t>
+          <t>Anne Morrow</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>V-2 Rocket</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What was the first object sold on eBay?</t>
+          <t>Which is the largest island in the world?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wristwatch</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Comic Book</t>
+          <t>New Guinea</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Laser Pointer</t>
+          <t>Greenland</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Who was the first President of the world’s first republic (USA)?</t>
+          <t>Which is the first country to make education compulsory by law?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>John Adams</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which was the first country to use paper money?</t>
+          <t>Which is the largest country in the world by area?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3251,577 +3251,577 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which is the smallest state in India by area?</t>
+          <t>Who was the first Prime Minister of the United Kingdom?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Winston Churchill</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Tony Blair</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Robert Walpole</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which was the first Indian satellite to orbit the Moon?</t>
+          <t>Which was the first Indian company listed on NASDAQ?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mangalyaan</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>INSAT</t>
+          <t>Satyam</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chandrayaan-1</t>
+          <t>Infosys</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
+          <t>What is the world’s tallest statue as of 2025?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>General V. K. Singh</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>General Manoj Pande</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Admiral Karambir Singh</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>General Bipin Rawat</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which is the world’s first country to ban tobacco completely?</t>
+          <t>Which is the largest bird in the world?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Emu</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Ostrich</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
+          <t>Which is the smallest bone in the human body?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Femur</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Tibia</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Stapes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ulna</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Gangtok</t>
+          <t>Stapes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>What was the first ever video uploaded to YouTube?</t>
+          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>Titanic</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Hello World</t>
+          <t>Avatar</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Test Video</t>
+          <t>Avengers: Endgame</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Launch Video</t>
+          <t>Oppenheimer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Me at the zoo</t>
+          <t>Avatar</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What was the world’s first printed book?</t>
+          <t>Which is the smallest country in the world by land area?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>The Holy Bible</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Quran</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>The Gutenberg Bible</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
+          <t>Which was the first messaging app?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IIT Delhi</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>IIT Bombay</t>
+          <t>ICQ</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>AIM</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>IIT Madras</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IIT Kharagpur</t>
+          <t>ICQ</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What was the world’s first search engine?</t>
+          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>Amartya Sen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AltaVista</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of India?</t>
+          <t>Which is the most used currency in the world?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sardar Patel</t>
+          <t>Yen</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>US Dollar</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Pound Sterling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>US Dollar</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which is the most downloaded app of all time?</t>
+          <t>What was the first ever video uploaded to YouTube?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Hello World</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Test Video</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Launch Video</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Me at the zoo</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which is the largest desert in the world?</t>
+          <t>What was the world’s first printed book?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sahara</t>
+          <t>The Holy Bible</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Gobi</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kalahari</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>Quran</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Antarctic Desert</t>
+          <t>The Gutenberg Bible</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a monorail?</t>
+          <t>Which was the first Indian Institute of Technology (IIT) established?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>IIT Delhi</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>IIT Bombay</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>IIT Madras</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>IIT Kharagpur</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Who was India’s first female President?</t>
+          <t>What was the world’s first search engine?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Archie</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sonia Gandhi</t>
+          <t>AltaVista</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Archie</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which is the first country to adopt a national flag?</t>
+          <t>Who was the first Prime Minister of India?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Sardar Patel</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of the United Kingdom?</t>
+          <t>Which is the most downloaded app of all time?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Margaret Thatcher</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tony Blair</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Robert Walpole</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -3831,312 +3831,312 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which was the first Indian company listed on NASDAQ?</t>
+          <t>Which is the largest desert in the world?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Sahara</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Gobi</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Kalahari</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Satyam</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Antarctic Desert</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What is the world’s tallest statue as of 2025?</t>
+          <t>Which is the first Indian city to have a monorail?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Statue of Liberty</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Spring Temple Buddha</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Christ the Redeemer</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Statue of Unity</t>
+          <t>Mumbai</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which is the largest bird in the world?</t>
+          <t>Who was India’s first female President?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Albatross</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Emu</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which is the smallest bone in the human body?</t>
+          <t>Which is the first country to adopt a national flag?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Femur</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tibia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ulna</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Stapes</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which is the highest-grossing movie of all time (worldwide)?</t>
+          <t>Which Indian monument has the highest number of tourist visits annually?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Titanic</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>Red Fort</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Avengers: Endgame</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Oppenheimer</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which is the smallest country in the world by land area?</t>
+          <t>Which was the first human-made object to reach space?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>V-2 Rocket</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which was the first messaging app?</t>
+          <t>What was the first object sold on eBay?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Wristwatch</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AIM</t>
+          <t>Comic Book</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ICQ</t>
+          <t>Laser Pointer</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Who was the first Indian to receive the Nobel Peace Prize?</t>
+          <t>Who was the first President of the world’s first republic (USA)?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>George Washington</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Amartya Sen</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>John Adams</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>George Washington</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which is the most used currency in the world?</t>
+          <t>Which was the first country to use paper money?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Yen</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pound Sterling</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>US Dollar</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -4146,1082 +4146,1082 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which country exports the most weapons?</t>
+          <t>Which is the smallest state in India by area?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Goa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>What was the first cloned mammal?</t>
+          <t>Which was the first Indian satellite to orbit the Moon?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Molly the Cow</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Polly the Pig</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kitty the Cat</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dolly the Sheep</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which religion has the most followers in the world?</t>
+          <t>Who was the first Indian Chief of Defence Staff (CDS)?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Islam</t>
+          <t>General V. K. Singh</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>General Manoj Pande</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Admiral Karambir Singh</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Christianity</t>
+          <t>General Bipin Rawat</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which city has the most skyscrapers (over 150m)?</t>
+          <t>Which is the world’s first country to ban tobacco completely?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Bhutan</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Which country has the highest number of Olympic medals overall?</t>
+          <t>Which Indian city was the first to be declared open defecation free (ODF)?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Gangtok</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Gangtok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which was the first country to legalize same-sex marriage?</t>
+          <t>Which river carries the most water by volume?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Yangtze</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Who was the first woman to fly solo around the world?</t>
+          <t>Which is the most spoken language in the world?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Valentina Tereshkova</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Anne Morrow</t>
+          <t>Mandarin</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Amelia Earhart</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which is the largest island in the world?</t>
+          <t>Which is the most spoken language in India?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>English</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>New Guinea</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Hindi</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which is the first country to make education compulsory by law?</t>
+          <t>Which was the first city to host the modern Olympic Games?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Athens</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which is the largest country in the world by area?</t>
+          <t>Which is the world's most visited heritage site?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Eiffel Tower</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Colosseum</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Great Wall of China</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which is the first country to launch a digital currency?</t>
+          <t>Which Indian state has the highest literacy rate?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Kerala</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which is the tallest animal in the world?</t>
+          <t>Which country has the highest population in the world?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Camel</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Moose</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>What was the first country to recognize the United States as independent?</t>
+          <t>Which is the first artificial satellite sent into space?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Apollo 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Vostok</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which country has the most UNESCO World Heritage Sites?</t>
+          <t>Who was the first Indian Miss World?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Sushmita Sen</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Lara Dutta</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Reita Faria</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Aishwarya Rai</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Reita Faria</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>What was the first successful vaccine developed for?</t>
+          <t>Which is the largest freshwater lake in the world by surface area?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Lake Victoria</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Lake Superior</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Polio</t>
+          <t>Lake Baikal</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>Lake Tanganyika</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>Lake Superior</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to have a fully underground metro network?</t>
+          <t>Which was the world's first artificial satellite?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Apollo 11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Explorer 1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Luna 2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Sputnik 1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which is the fastest bird in the world?</t>
+          <t>Which is the largest dam in India by volume?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Golden Eagle</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Sardar Sarovar Dam</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>Bhakra Nangal</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Swan</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Peregrine Falcon</t>
+          <t>Hirakud Dam</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to implement the GST?</t>
+          <t>What was the first website ever created?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Google.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Wikipedia.org</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>CERN.ch</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>info.cern.ch</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which Indian river got the status of ‘living entity’ first?</t>
+          <t>Which was the first Indian film to win an Oscar?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Slumdog Millionaire</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Gandhi</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which is the highest waterfall in the world?</t>
+          <t>Who was the first person to go to space?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Niagara Falls</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tugela Falls</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Yosemite Falls</t>
+          <t>John Glenn</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Angel Falls</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank to launch an ATM?</t>
+          <t>Which is the most downloaded game of all time?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>PUBG</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Candy Crush</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ICICI</t>
+          <t>Minecraft</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Subway Surfers</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which was the first movie with sound (talkie)?</t>
+          <t>Which was the first nation to reach the South Pole?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>King Kong</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>The Jazz Singer</t>
+          <t>Norway</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which was the first Indian communication satellite?</t>
+          <t>Which is the world’s first university?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Nalanda</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Takshashila</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>APPLESAT</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>INSAT-2A</t>
+          <t>Al-Qarawiyyin</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Takshashila</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which country produces the most oil?</t>
+          <t>Which is the largest continent by land area?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Who invented the first telephone?</t>
+          <t>Which mobile phone brand sells the most globally?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Thomas Edison</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Guglielmo Marconi</t>
+          <t>Oppo</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alexander Graham Bell</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Who was the first President of India?</t>
+          <t>Which is the deepest ocean in the world?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Atlantic Ocean</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Indian Ocean</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dr. S. Radhakrishnan</t>
+          <t>Arctic Ocean</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Pacific Ocean</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Which is the richest company in the world by market value (2025)?</t>
+          <t>What was the first country to ban plastic bags nationwide?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Saudi Aramco</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Rwanda</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>What was the world's first message sent over the internet?</t>
+          <t>Which country has the most UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>What was the name of the first computer virus?</t>
+          <t>Which country launched the world's first satellite?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ILOVEYOU</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stuxnet</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>WannaCry</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Creeper</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Which is the most populated city in the world?</t>
+          <t>Which is the longest railway platform in the world?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Gorakhpur</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Kharagpur</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Hubballi</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Howrah</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Hubballi</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Which is the world’s first democracy?</t>
+          <t>Which is India’s first indigenously built aircraft carrier?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>INS Viraat</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>INS Arihant</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>INS Trikand</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Athens</t>
+          <t>INS Vikrant</t>
         </is>
       </c>
     </row>
@@ -5231,697 +5231,697 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which country has the longest coastline?</t>
+          <t>Who invented the first airplane?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Leonardo da Vinci</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Amelia Earhart</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Charles Lindbergh</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Wright Brothers</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which is the oldest dam in India still in use?</t>
+          <t>Who was the first person to step on the Moon?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mettur Dam</t>
+          <t>Buzz Aldrin</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Krishna Raja Sagara Dam</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Yuri Gagarin</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hirakud Dam</t>
+          <t>Michael Collins</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Kallanai Dam</t>
+          <t>Neil Armstrong</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which country has the most nuclear weapons as of 2025?</t>
+          <t>Which country has the highest number of billionaires?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Which is the largest ocean in the world by area?</t>
+          <t>Who invented the first electric light bulb?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Atlantic Ocean</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Arctic Ocean</t>
+          <t>Michael Faraday</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Indian Ocean</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pacific Ocean</t>
+          <t>Thomas Edison</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which is the deepest lake in the world?</t>
+          <t>Which country has the most lakes?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Lake Superior</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Lake Tanganyika</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Caspian Sea</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lake Baikal</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Who was the first person to win two Nobel Prizes?</t>
+          <t>Which Indian city is the first to use electric buses at scale?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Albert Einstein</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Linus Pauling</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Erwin Schrödinger</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Pune</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which was the first Indian express train?</t>
+          <t>Which is the first country to implement a constitution?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Shatabdi Express</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Rajdhani Express</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Duronto Express</t>
+          <t>France</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Deccan Queen</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Which Indian state was the first to achieve 100% literacy?</t>
+          <t>Which planet has the most moons?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Saturn</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Who was the first woman ruler of India?</t>
+          <t>Which is the world’s first programmable computer?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Rani Lakshmibai</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>Colossus</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ahilyabai Holkar</t>
+          <t>Z3</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Razia Sultana</t>
+          <t>Z3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Which was the first animated feature film?</t>
+          <t>Which is the largest volcano in the world (by volume)?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Mount Fuji</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Cinderella</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Pinocchio</t>
+          <t>Eyjafjallajökull</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bambi</t>
+          <t>Mount Etna</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Snow White and the Seven Dwarfs</t>
+          <t>Mauna Loa</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Who was the first woman to win a Nobel Prize?</t>
+          <t>Which is the largest state in India by area?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Rosalind Franklin</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Rajasthan</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a Nobel Prize?</t>
+          <t>Which country has the highest GDP in the world?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>C.V. Raman</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which is the world's first language (known oldest)?</t>
+          <t>What is India’s first nuclear reactor called?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Dhruva</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>KAMINI</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Apsara</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>CIRUS</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sumerian</t>
+          <t>Apsara</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>What is the name of India’s first satellite?</t>
+          <t>Which is the smallest continent by land area?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Chandrayaan</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Which Indian was the first to win an Olympic gold medal?</t>
+          <t>Which was the first car manufacturing company?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Major Dhyan Chand</t>
+          <t>Peugeot</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KD Jadhav</t>
+          <t>Rolls-Royce</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Abhinav Bindra</t>
+          <t>Peugeot</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Which is the highest mountain peak in the world?</t>
+          <t>Which Indian city is known as the "first Smart City"?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Gandhinagar</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Makalu</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Which is the longest river in the world?</t>
+          <t>Which was the first country to grant women the right to vote?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Yangtze</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Who was the first human in space?</t>
+          <t>Which is India’s first supercomputer?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Neil Armstrong</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Buzz Aldrin</t>
+          <t>Shakti</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>Virgo</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>John Glenn</t>
+          <t>Mihir</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Yuri Gagarin</t>
+          <t>PARAM 8000</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Which is the first Indian bank?</t>
+          <t>Which is the coldest place on Earth?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>Siberia</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Vostok Station</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Allahabad Bank</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bank of Bombay</t>
+          <t>Vostok Station</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Which is the world's first novel ever written?</t>
+          <t>Which country has the most volcanoes?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Don Quixote</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Beowulf</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>The Tale of Genji</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -5931,312 +5931,312 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Which is the largest mammal in the world?</t>
+          <t>Which is the most visited city in the world (tourism)?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>African Elephant</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Giraffe</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hippopotamus</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Blue Whale</t>
+          <t>Paris</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Which Indian airport is the busiest by passenger traffic?</t>
+          <t>What was the first smartphone ever made?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Chhatrapati Shivaji Intl (Mumbai)</t>
+          <t>IBM Simon</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kempegowda Intl (Bangalore)</t>
+          <t>Nokia 3310</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi Intl (Hyderabad)</t>
+          <t>Motorola DynaTAC</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Indira Gandhi Intl (Delhi)</t>
+          <t>IBM Simon</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Which country has the largest economy (GDP)?</t>
+          <t>Which was the first Indian movie submitted for the Oscars?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Lagaan</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mother India</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mother India</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Who was the first person to receive Bharat Ratna?</t>
+          <t>Who is the first Indian to climb Mount Everest?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>S. Radhakrishnan</t>
+          <t>Bachendri Pal</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Tenzing Norgay</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Santosh Yadav</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>C. Rajagopalachari</t>
+          <t>Avtar Singh Cheema</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which Indian river has the largest length within India?</t>
+          <t>Which is the world's first man-made nuclear reactor?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Fermi-1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>DIDO</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Brahmaputra</t>
+          <t>THTR-300</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Chicago Pile-1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which country is the largest producer of gold?</t>
+          <t>Which is the tallest statue in the world?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Spring Temple Buddha</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Christ the Redeemer</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Statue of Liberty</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Statue of Unity</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the 'City of Lakes'?</t>
+          <t>Which Indian state hosted the first International G20 summit in India?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Who was the first Indian in space?</t>
+          <t>Which is the hottest planet in the solar system?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Venus</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Which was the first programming language?</t>
+          <t>Which is the first Indian mission to Mars?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>COBOL</t>
+          <t>Chandrayaan-1</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>INSAT</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>IRNSS</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fortran</t>
+          <t>Mangalyaan</t>
         </is>
       </c>
     </row>
@@ -6246,32 +6246,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Which is the smallest mammal by weight?</t>
+          <t>What was the first computer called?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>ENIAC</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Pygmy Shrew</t>
+          <t>UNIVAC</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mouse Lemur</t>
+          <t>IBM 1401</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Pygmy Possum</t>
+          <t>Apple I</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Bumblebee Bat</t>
+          <t>ENIAC</t>
         </is>
       </c>
     </row>
@@ -6281,242 +6281,242 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Which country has the highest literacy rate?</t>
+          <t>Which planet is closest to Earth most often?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Mercury</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>What was the first biosphere reserve in India?</t>
+          <t>Who was the first Indian Governor-General of independent India?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Sundarbans</t>
+          <t>Lord Mountbatten</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Nanda Devi</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Manas</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Nilgiri</t>
+          <t>C. Rajagopalachari</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman in space?</t>
+          <t>Which animal is considered the fastest on land?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Sunita Williams</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ritu Karidhal</t>
+          <t>Greyhound</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Kalpana Chawla</t>
+          <t>Cheetah</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which bird is believed to be extinct due to human activity?</t>
+          <t>Which is the world’s oldest living city?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Penguin</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Bald Eagle</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>Athens</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dodo</t>
+          <t>Varanasi</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Which is the largest species of shark?</t>
+          <t>Which was the first Indian film?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tiger Shark</t>
+          <t>Alam Ara</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Hammerhead Shark</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>Sholay</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Great White Shark</t>
+          <t>Pather Panchali</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Whale Shark</t>
+          <t>Raja Harishchandra</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Who was the first Indian female IPS officer?</t>
+          <t>Who was the first female Prime Minister of India?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Anu Singh</t>
+          <t>Sonia Gandhi</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Radhika Kumari</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Pooja Thakur</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Kiran Bedi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Which is the first Indian city to get an underground metro?</t>
+          <t>Which country has the smallest population?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Vatican City</t>
         </is>
       </c>
     </row>
@@ -6526,417 +6526,417 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Who was the first Indian cricketer to score a triple century in Test cricket?</t>
+          <t>Who was the first woman Prime Minister in the world?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Sunil Gavaskar</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Golda Meir</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sachin Tendulkar</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rahul Dravid</t>
+          <t>Margaret Thatcher</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Virender Sehwag</t>
+          <t>Sirimavo Bandaranaike</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Which language has the most native speakers in the world?</t>
+          <t>Which country has the most time zones (including territories)?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Mandarin Chinese</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Mandarin Chinese</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Which is the largest mosque in India?</t>
+          <t>Which is the smallest bird in the world?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jama Masjid, Delhi</t>
+          <t>Hummingbird</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Mecca Masjid, Hyderabad</t>
+          <t>Parakeet</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nakhoda Masjid, Kolkata</t>
+          <t>Finch</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Taj-ul-Masajid, Bhopal</t>
+          <t>Hummingbird</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>What was the first video game ever created?</t>
+          <t>Which country has the largest forest area in the world?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Pong</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Pac-Man</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tetris</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tennis for Two</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>What was the first email ever sent?</t>
+          <t>Which was the first country to reach Mars orbit successfully?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Login123</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>QWERTYUIOP</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Who was the first woman to receive a Nobel Prize in two different sciences?</t>
+          <t>What was the first online shopping site?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ada Lovelace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Dorothy Hodgkin</t>
+          <t>NetMarket</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lise Meitner</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Marie Curie</t>
+          <t>NetMarket</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Which was the first war of Indian independence?</t>
+          <t>Which city is known as the "Silicon Valley of India"?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Battle of Plassey</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Battle of Panipat</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Champaran Movement</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>1857 Revolt</t>
+          <t>Bangalore</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which is the busiest airport in the world by passenger volume?</t>
+          <t>Which was the first Indian city to be electrified?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Beijing Capital</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Atlanta (ATL)</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Heathrow</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Dubai Intl</t>
+          <t>Darjeeling</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Atlanta (ATL)</t>
+          <t>Darjeeling</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a gold medal in athletics at CWG?</t>
+          <t>Which is the longest national highway in India?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>NH44</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Neeraj Chopra</t>
+          <t>NH7</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Hima Das</t>
+          <t>NH27</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Anju George</t>
+          <t>NH19</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milkha Singh</t>
+          <t>NH44</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Which country has the largest number of active military personnel?</t>
+          <t>Which was the first Indian state formed on linguistic basis?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Who was the first Indian woman to win a medal at the Olympics?</t>
+          <t>Which is the tallest building in the world?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>Shanghai Tower</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Saina Nehwal</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P. V. Sindhu</t>
+          <t>Merdeka 118</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mary Kom</t>
+          <t>One World Trade Center</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Karnam Malleswari</t>
+          <t>Burj Khalifa</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which is the first Indian state to ban plastic completely?</t>
+          <t>Which Indian state launched the first electric vehicle policy?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Sikkim</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Kerala</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Himachal Pradesh</t>
-        </is>
-      </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Karnataka</t>
         </is>
       </c>
     </row>
